--- a/Assets/test260903/chapter0203.xlsx
+++ b/Assets/test260903/chapter0203.xlsx
@@ -1,12 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="197" documentId="11_E10EE94338F254052E83A027A8BF203497349031" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F3E973B-4125-4B1F-9CB0-1DCDE6B50D1A}"/>
+  <bookViews>
+    <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="chapter0203" sheetId="1" r:id="rId4"/>
+    <sheet name="chapter0203" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
       <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId5" roundtripDataChecksum="1wnk63aERf7/uTyT6okFjiq/Ayajw31Os+0y4XC6imY="/>
@@ -16,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="100">
   <si>
     <t>Command</t>
   </si>
@@ -66,9 +75,6 @@
     <t>WaitInput</t>
   </si>
   <si>
-    <t>BgOff</t>
-  </si>
-  <si>
     <t>Chapter2-3です</t>
   </si>
   <si>
@@ -76,27 +82,422 @@
   </si>
   <si>
     <t>*chapter0204_Start</t>
+  </si>
+  <si>
+    <t>車は、美鈴さんの拠点へ走っている。
+装備品を補給するためだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>背景：車内（ハマー）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>FadeIn</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>black</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Se</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>車の走行</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>それにしても……最悪の事態になった。
+まさか身内に裏切られるなんて</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>僕は社長の息子だ。
+将来を約束された立場だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でも、だからこそ邪魔に思う輩もいる。
+僕がいる限り、出世できないヤツもいる</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>「邪魔者は排除する」
+これは組織運営と商売の基本だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>しかし、どうして叔父が僕を？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>いや、叔父だけじゃないかもしれない。
+他の親戚や、父さんだって……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>鈴野美鈴</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>通常</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>主人公</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>お～～い</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そもそも僕が北九州に派遣されたのは、
+父さんの命令だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>叔父が父さんの命令に従っている
+可能性だって十分にある</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>お～～いってば</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>父さんには動機もある。
+何せ僕は「前妻の子」だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>父さんとあの女は、
+次期社長の座に弟たちを推している</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>争いを避けるためなら、
+事前に僕を消してしまうのが最善……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>イテ！！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>殴打（ゲンコツ）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Shake</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Camera</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>x=3.</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>な～～に難しい顔してんの、エロガキ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>怒り</t>
+    <rPh sb="0" eb="1">
+      <t>イカ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Selection</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-1-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>イチイチ殴らないでください！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アタシがずっと声をかけてるのに、
+無視をするからだろ！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-2-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>叔父に殺されかけたんですよ！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だから？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-3-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>叔父ですよ！　叔父！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-4-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>悩んで当然でしょうが！！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そんなことで悩んでどうすんよ？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-5-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そんなこと！？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>うん、そんなことだよ。
+よくあることじゃん、そういうの</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>つーかさ、
+裏切られた後に悩んでも仕方ないよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>大事なのは裏切られた後に、
+どうケジメをつけるか</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>エロガキ、よく聞いて</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アタシはガキの頃、両親に裏切られた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>悲しみ</t>
+    <rPh sb="0" eb="1">
+      <t>カナ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>両親は薬の取引に手を出して、
+東南アジアの連中を怒らせた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>その時、ガキのアタシを差し出した。
+「これを金に換えて」って</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>もちろん親はそのまま殺されて、
+アタシも売られたんだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-6-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……最悪ですね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でもよ、その売られた先が良かった。
+今のアタシが入ってる組織で……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>喜び</t>
+    <rPh sb="0" eb="1">
+      <t>ヨロコ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>「白蛇」ってマフィアでさ、
+そこで暗殺の訓練を受けたんだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>おかげで強くなって、ガキの頃の仇の
+東南アジアの連中は皆殺しにできた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>結果オーライっていうか、
+むしろ今の方が絶対に幸せ！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>って、断言できる</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ま、そんな感じだからさ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>人生、何とかなるもんだよ。
+親戚に裏切られたくらい気にすんな</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>無茶苦茶だけど……
+美鈴さんの意見も一理ある</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>僕は裏切られた。
+けれど、まだこうして生きている</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>考えるべきことは、どう振る舞うかだ。
+どうやって生き残るかだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>安全を確保して、
+生き残る方法を考える方がいい</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>エロガキ、どうよ？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Jump</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-7-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-7-ｂ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>了解です</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>とはいえ、あなたの理屈はおかしい</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>それでいい。
+落ち込まずに、先のことを考えよっ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-7合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そうかな？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ま、ともかく何とかなるもんだよ。</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>何せアタシが味方についてんだからさ。
+エロガキは余計な心配しなくていいから</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>そういえば……何故この人は、
+ここまでするのだろうか？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴さんは戦闘狂だ。
+人を撃っている時、ずっと笑っていた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>戦いにハンデを持ち込むあたり、
+死闘を自ら望んでいるようにも感じる</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でも、それだけじゃない。
+あのロシア人との会話では……</t>
+    <phoneticPr fontId="4"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="MS PGothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -104,49 +505,65 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="10">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -336,28 +753,28 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-  <sheetPr>
-    <pageSetUpPr/>
-  </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:L1063"/>
+  <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="11.5"/>
-    <col customWidth="1" min="2" max="2" width="14.0"/>
-    <col customWidth="1" min="3" max="7" width="5.13"/>
-    <col customWidth="1" min="8" max="8" width="8.63"/>
-    <col customWidth="1" min="9" max="9" width="37.75"/>
-    <col customWidth="1" min="10" max="10" width="8.25"/>
-    <col customWidth="1" min="11" max="11" width="6.0"/>
-    <col customWidth="1" min="12" max="12" width="11.38"/>
-    <col customWidth="1" min="13" max="26" width="8.0"/>
+    <col min="1" max="1" width="11.44140625" customWidth="1"/>
+    <col min="2" max="2" width="14" customWidth="1"/>
+    <col min="3" max="7" width="5.109375" customWidth="1"/>
+    <col min="8" max="8" width="8.6640625" customWidth="1"/>
+    <col min="9" max="9" width="37.77734375" customWidth="1"/>
+    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="11" max="11" width="6" customWidth="1"/>
+    <col min="12" max="12" width="11.33203125" customWidth="1"/>
+    <col min="13" max="26" width="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.5" customHeight="1">
+    <row r="1" spans="1:12" ht="13.5" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -395,670 +812,1082 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="13.5" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A2" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B2" s="1"/>
       <c r="H2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" ht="13.5" customHeight="1">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
       <c r="I3" s="1"/>
     </row>
-    <row r="4" ht="13.5" customHeight="1">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="6">
-        <v>3.0</v>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="4">
+        <v>3</v>
       </c>
       <c r="I4" s="1"/>
     </row>
-    <row r="5" ht="13.5" customHeight="1">
-      <c r="A5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4"/>
+    <row r="5" spans="1:12" ht="13.5" customHeight="1">
       <c r="H5" s="4"/>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-    </row>
-    <row r="6" ht="13.5" customHeight="1">
-      <c r="B6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="K6" s="1"/>
-    </row>
-    <row r="7" ht="13.5" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    </row>
+    <row r="6" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="1"/>
+    </row>
+    <row r="8" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="K8" s="1"/>
+    </row>
+    <row r="9" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="K9" s="1"/>
+    </row>
+    <row r="10" spans="1:12" ht="30" customHeight="1">
+      <c r="B10" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H10" s="1"/>
+      <c r="I10" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" ht="13.5" customHeight="1">
-      <c r="I8" s="1"/>
-    </row>
-    <row r="9" ht="13.5" customHeight="1">
-      <c r="I9" s="1"/>
-    </row>
-    <row r="10" ht="13.5" customHeight="1">
-      <c r="I10" s="1"/>
-    </row>
-    <row r="11" ht="13.5" customHeight="1">
-      <c r="I11" s="1"/>
-    </row>
-    <row r="12" ht="13.5" customHeight="1">
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-    </row>
-    <row r="13" ht="13.5" customHeight="1">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-    </row>
-    <row r="14" ht="13.5" customHeight="1">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-    </row>
-    <row r="15" ht="13.5" customHeight="1">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="I15" s="1"/>
+    </row>
+    <row r="11" spans="1:12" ht="30.6" customHeight="1">
+      <c r="B11" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I11" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="28.2" customHeight="1">
+      <c r="B12" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I12" s="5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="30" customHeight="1">
+      <c r="B13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I13" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="31.2" customHeight="1">
+      <c r="B14" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="13.5" customHeight="1">
+      <c r="B15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I15" s="5" t="s">
+        <v>29</v>
+      </c>
       <c r="J15" s="1"/>
     </row>
-    <row r="16" ht="13.5" customHeight="1">
-      <c r="B16" s="1"/>
+    <row r="16" spans="1:12" ht="28.2" customHeight="1">
+      <c r="A16" s="1"/>
+      <c r="B16" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="C16" s="1"/>
-      <c r="I16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="I16" s="5" t="s">
+        <v>30</v>
+      </c>
       <c r="J16" s="1"/>
     </row>
-    <row r="17" ht="13.5" customHeight="1">
+    <row r="17" spans="1:10" ht="13.5" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="I17" s="1"/>
-    </row>
-    <row r="18" ht="13.5" customHeight="1">
+      <c r="B17" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I17" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="1:10" ht="28.8" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="I18" s="1"/>
-    </row>
-    <row r="19" ht="13.5" customHeight="1">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="I19" s="1"/>
-    </row>
-    <row r="20" ht="13.5" customHeight="1">
+      <c r="B18" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C18" s="1"/>
+      <c r="I18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B19" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="1"/>
+      <c r="I19" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="1:10" ht="13.5" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-    </row>
-    <row r="21" ht="13.5" customHeight="1">
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="I21" s="1"/>
-    </row>
-    <row r="22" ht="13.5" customHeight="1">
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="I22" s="1"/>
-    </row>
-    <row r="23" ht="13.5" customHeight="1">
+      <c r="B20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A21" s="1"/>
+      <c r="B21" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I21" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A22" s="1"/>
+      <c r="B22" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I22" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="28.2" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-    </row>
-    <row r="24" ht="13.5" customHeight="1">
-      <c r="A24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-    </row>
-    <row r="25" ht="13.5" customHeight="1">
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="I25" s="1"/>
-    </row>
-    <row r="26" ht="13.5" customHeight="1">
-      <c r="B26" s="1"/>
+      <c r="B23" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" s="1"/>
+      <c r="I23" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A24" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="H24" s="1"/>
+      <c r="I24" s="5"/>
+    </row>
+    <row r="25" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H25" s="1"/>
+      <c r="I25" s="5"/>
+    </row>
+    <row r="26" spans="1:10" ht="13.8" customHeight="1">
+      <c r="B26" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="C26" s="1"/>
-      <c r="I26" s="1"/>
-    </row>
-    <row r="27" ht="13.5" customHeight="1">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-    </row>
-    <row r="28" ht="13.5" customHeight="1">
-      <c r="A28" s="1"/>
-      <c r="I28" s="1"/>
+      <c r="I26" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B27" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I27" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A28" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="I28" s="5" t="s">
+        <v>50</v>
+      </c>
       <c r="J28" s="1"/>
     </row>
-    <row r="29" ht="13.5" customHeight="1">
+    <row r="29" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="I29" s="1"/>
-    </row>
-    <row r="30" ht="13.5" customHeight="1">
-      <c r="I30" s="1"/>
-    </row>
-    <row r="31" ht="13.5" customHeight="1">
-      <c r="I31" s="1"/>
-    </row>
-    <row r="32" ht="13.5" customHeight="1">
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="30" customHeight="1">
+      <c r="B30" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="I30" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A31" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C31" s="1"/>
+      <c r="I31" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A32" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" s="1"/>
       <c r="I32" s="1"/>
-    </row>
-    <row r="33" ht="13.5" customHeight="1">
-      <c r="I33" s="1"/>
-    </row>
-    <row r="34" ht="13.5" customHeight="1">
-      <c r="I34" s="1"/>
-    </row>
-    <row r="35" ht="13.5" customHeight="1">
+      <c r="J32" s="1"/>
+    </row>
+    <row r="33" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A33" s="1"/>
+      <c r="B33" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A34" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I34" s="5" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A35" s="1" t="s">
+        <v>55</v>
+      </c>
       <c r="I35" s="1"/>
     </row>
-    <row r="36" ht="13.5" customHeight="1">
-      <c r="I36" s="1"/>
-    </row>
-    <row r="37" ht="13.5" customHeight="1">
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="I37" s="1"/>
-    </row>
-    <row r="38" ht="13.5" customHeight="1">
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
+    <row r="36" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B36" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I36" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A37" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I37" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A38" s="1" t="s">
+        <v>57</v>
+      </c>
       <c r="I38" s="1"/>
     </row>
-    <row r="39" ht="13.5" customHeight="1">
-      <c r="I39" s="1"/>
-    </row>
-    <row r="40" ht="13.5" customHeight="1">
-      <c r="I40" s="1"/>
-    </row>
-    <row r="41" ht="13.5" customHeight="1">
+    <row r="39" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A40" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="I40" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A41" s="1" t="s">
+        <v>60</v>
+      </c>
       <c r="I41" s="1"/>
     </row>
-    <row r="42" ht="13.5" customHeight="1">
-      <c r="I42" s="1"/>
-    </row>
-    <row r="43" ht="13.5" customHeight="1">
-      <c r="I43" s="1"/>
-    </row>
-    <row r="44" ht="13.5" customHeight="1">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="I44" s="1"/>
-    </row>
-    <row r="45" ht="13.5" customHeight="1">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="I45" s="1"/>
-    </row>
-    <row r="46" ht="13.5" customHeight="1">
-      <c r="A46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-    </row>
-    <row r="47" ht="13.5" customHeight="1">
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="I47" s="1"/>
-    </row>
-    <row r="48" ht="13.5" customHeight="1">
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-    </row>
-    <row r="49" ht="13.5" customHeight="1">
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-    </row>
-    <row r="50" ht="13.5" customHeight="1">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-    </row>
-    <row r="51" ht="13.5" customHeight="1">
-      <c r="A51" s="1"/>
+    <row r="42" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B42" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B43" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I43" s="5" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="30" customHeight="1">
+      <c r="B44" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I44" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B45" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I45" s="5" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B46" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I46" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B47" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B48" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I48" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="31.2" customHeight="1">
+      <c r="A49" s="1"/>
+      <c r="B49" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I49" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A50" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A51" s="1" t="s">
+        <v>71</v>
+      </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" ht="13.5" customHeight="1">
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="I52" s="1"/>
-    </row>
-    <row r="53" ht="13.5" customHeight="1">
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="I53" s="1"/>
-    </row>
-    <row r="54" ht="13.5" customHeight="1">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="I54" s="1"/>
-    </row>
-    <row r="55" ht="13.5" customHeight="1">
+    <row r="52" spans="1:10" ht="31.8" customHeight="1">
+      <c r="B52" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I52" s="5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B53" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I53" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="J53" s="1"/>
+    </row>
+    <row r="54" spans="1:10" ht="31.2" customHeight="1">
+      <c r="B54" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I54" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="J54" s="1"/>
+    </row>
+    <row r="55" spans="1:10" ht="30" customHeight="1">
       <c r="A55" s="1"/>
-      <c r="I55" s="1"/>
-    </row>
-    <row r="56" ht="13.5" customHeight="1">
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" ht="13.5" customHeight="1">
-      <c r="I57" s="1"/>
-    </row>
-    <row r="58" ht="13.5" customHeight="1">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="I58" s="1"/>
-    </row>
-    <row r="59" ht="13.5" customHeight="1">
+      <c r="B55" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I55" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="J55" s="1"/>
+    </row>
+    <row r="56" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A56" s="1"/>
+      <c r="B56" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I56" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J56" s="1"/>
+    </row>
+    <row r="57" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B57" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I57" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10" ht="30" customHeight="1">
+      <c r="B58" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I58" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10" ht="28.2" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="I59" s="1"/>
-    </row>
-    <row r="60" ht="13.5" customHeight="1">
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="I60" s="1"/>
-    </row>
-    <row r="61" ht="13.5" customHeight="1">
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="I61" s="1"/>
-    </row>
-    <row r="62" ht="13.5" customHeight="1">
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="I62" s="1"/>
-    </row>
-    <row r="63" ht="13.5" customHeight="1">
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="I63" s="1"/>
-    </row>
-    <row r="64" ht="13.5" customHeight="1">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="I64" s="1"/>
-    </row>
-    <row r="65" ht="13.5" customHeight="1">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-    </row>
-    <row r="66" ht="13.5" customHeight="1">
+      <c r="B59" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="30" customHeight="1">
+      <c r="A60" s="1"/>
+      <c r="B60" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I60" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B61" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I61" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B62" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I62" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A63" s="1"/>
+      <c r="B63" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A64" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="I64" s="5" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A65" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C65" s="1"/>
+      <c r="I65" s="5" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A66" s="1" t="s">
+        <v>87</v>
+      </c>
       <c r="B66" s="1"/>
       <c r="C66" s="1"/>
       <c r="I66" s="1"/>
     </row>
-    <row r="67" ht="13.5" customHeight="1">
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="I67" s="1"/>
-    </row>
-    <row r="68" ht="13.5" customHeight="1">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
+    <row r="67" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B67" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C67" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I67" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A68" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C68" s="1"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" ht="13.5" customHeight="1">
-      <c r="A69" s="1"/>
+    <row r="69" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A69" s="1" t="s">
+        <v>88</v>
+      </c>
       <c r="B69" s="1"/>
-      <c r="H69" s="1"/>
       <c r="I69" s="1"/>
     </row>
-    <row r="70" ht="13.5" customHeight="1">
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="I70" s="1"/>
-    </row>
-    <row r="71" ht="13.5" customHeight="1">
-      <c r="B71" s="1"/>
+    <row r="70" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A70" s="1"/>
+      <c r="B70" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C70" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A71" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="C71" s="1"/>
       <c r="I71" s="1"/>
     </row>
-    <row r="72" ht="13.5" customHeight="1">
+    <row r="72" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A72" s="1" t="s">
+        <v>92</v>
+      </c>
       <c r="B72" s="1"/>
       <c r="C72" s="1"/>
       <c r="I72" s="1"/>
     </row>
-    <row r="73" ht="13.5" customHeight="1">
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="I73" s="1"/>
-    </row>
-    <row r="74" ht="13.5" customHeight="1">
-      <c r="B74" s="1"/>
-      <c r="C74" s="1"/>
-      <c r="I74" s="1"/>
-    </row>
-    <row r="75" ht="13.5" customHeight="1">
-      <c r="B75" s="1"/>
+    <row r="73" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A73" s="1"/>
+      <c r="B73" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="I73" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A74" s="1"/>
+      <c r="B74" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="H74" s="1"/>
+      <c r="I74" s="5" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9" ht="31.8" customHeight="1">
+      <c r="B75" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="C75" s="1"/>
-      <c r="I75" s="1"/>
-    </row>
-    <row r="76" ht="13.5" customHeight="1">
-      <c r="B76" s="1"/>
+      <c r="I75" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" ht="30" customHeight="1">
+      <c r="B76" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="C76" s="1"/>
-      <c r="I76" s="1"/>
-    </row>
-    <row r="77" ht="13.5" customHeight="1">
-      <c r="B77" s="1"/>
+      <c r="I76" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B77" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="C77" s="1"/>
-      <c r="I77" s="1"/>
-    </row>
-    <row r="78" ht="13.5" customHeight="1">
-      <c r="B78" s="1"/>
+      <c r="I77" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="28.2" customHeight="1">
+      <c r="B78" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="C78" s="1"/>
-      <c r="I78" s="1"/>
-      <c r="J78" s="1"/>
-    </row>
-    <row r="79" ht="13.5" customHeight="1">
+      <c r="I78" s="5" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
       <c r="I79" s="1"/>
     </row>
-    <row r="80" ht="13.5" customHeight="1">
+    <row r="80" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
       <c r="I80" s="1"/>
     </row>
-    <row r="81" ht="13.5" customHeight="1">
+    <row r="81" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
       <c r="I81" s="1"/>
     </row>
-    <row r="82" ht="13.5" customHeight="1">
-      <c r="A82" s="1"/>
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
       <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
       <c r="I82" s="1"/>
-      <c r="J82" s="1"/>
-    </row>
-    <row r="83" ht="13.5" customHeight="1">
-      <c r="A83" s="1"/>
+    </row>
+    <row r="83" spans="1:10" ht="13.5" customHeight="1">
       <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
       <c r="I83" s="1"/>
       <c r="J83" s="1"/>
     </row>
-    <row r="84" ht="13.5" customHeight="1">
-      <c r="A84" s="1"/>
-    </row>
-    <row r="85" ht="13.5" customHeight="1">
-      <c r="B85" s="1"/>
-      <c r="C85" s="1"/>
+    <row r="84" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="1:10" ht="13.5" customHeight="1">
       <c r="I85" s="1"/>
     </row>
-    <row r="86" ht="13.5" customHeight="1">
-      <c r="B86" s="1"/>
-      <c r="C86" s="1"/>
+    <row r="86" spans="1:10" ht="13.5" customHeight="1">
       <c r="I86" s="1"/>
     </row>
-    <row r="87" ht="13.5" customHeight="1">
+    <row r="87" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A87" s="1"/>
       <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
       <c r="I87" s="1"/>
-    </row>
-    <row r="88" ht="13.5" customHeight="1">
+      <c r="J87" s="1"/>
+    </row>
+    <row r="88" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A88" s="1"/>
       <c r="B88" s="1"/>
-      <c r="C88" s="1"/>
       <c r="I88" s="1"/>
-    </row>
-    <row r="89" ht="13.5" customHeight="1">
+      <c r="J88" s="1"/>
+    </row>
+    <row r="89" spans="1:10" ht="13.5" customHeight="1">
       <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
-    </row>
-    <row r="90" ht="13.5" customHeight="1">
-      <c r="A90" s="1"/>
-    </row>
-    <row r="91" ht="13.5" customHeight="1">
+    </row>
+    <row r="90" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B90" s="1"/>
+      <c r="C90" s="1"/>
+      <c r="I90" s="1"/>
+    </row>
+    <row r="91" spans="1:10" ht="13.5" customHeight="1">
       <c r="B91" s="1"/>
       <c r="C91" s="1"/>
       <c r="I91" s="1"/>
     </row>
-    <row r="92" ht="13.5" customHeight="1">
+    <row r="92" spans="1:10" ht="13.5" customHeight="1">
       <c r="B92" s="1"/>
       <c r="C92" s="1"/>
       <c r="I92" s="1"/>
     </row>
-    <row r="93" ht="13.5" customHeight="1">
+    <row r="93" spans="1:10" ht="13.5" customHeight="1">
       <c r="B93" s="1"/>
       <c r="C93" s="1"/>
       <c r="I93" s="1"/>
     </row>
-    <row r="94" ht="13.5" customHeight="1">
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A94" s="1"/>
       <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="I94" s="1"/>
-    </row>
-    <row r="95" ht="13.5" customHeight="1">
+    </row>
+    <row r="95" spans="1:10" ht="13.5" customHeight="1">
       <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-    </row>
-    <row r="96" ht="13.5" customHeight="1">
-      <c r="A96" s="1"/>
-    </row>
-    <row r="97" ht="13.5" customHeight="1">
+    </row>
+    <row r="96" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B96" s="1"/>
+      <c r="C96" s="1"/>
+      <c r="I96" s="1"/>
+    </row>
+    <row r="97" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B97" s="1"/>
+      <c r="C97" s="1"/>
       <c r="I97" s="1"/>
     </row>
-    <row r="98" ht="13.5" customHeight="1">
+    <row r="98" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B98" s="1"/>
+      <c r="C98" s="1"/>
       <c r="I98" s="1"/>
     </row>
-    <row r="99" ht="13.5" customHeight="1">
-      <c r="A99" s="1"/>
+    <row r="99" spans="1:9" ht="13.5" customHeight="1">
       <c r="B99" s="1"/>
+      <c r="C99" s="1"/>
       <c r="I99" s="1"/>
     </row>
-    <row r="100" ht="13.5" customHeight="1">
+    <row r="100" spans="1:9" ht="13.5" customHeight="1">
       <c r="A100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-    </row>
-    <row r="101" ht="13.5" customHeight="1">
-      <c r="B101" s="1"/>
-      <c r="C101" s="1"/>
-      <c r="I101" s="1"/>
-    </row>
-    <row r="102" ht="13.5" customHeight="1">
-      <c r="B102" s="1"/>
-      <c r="C102" s="1"/>
+      <c r="B100" s="1"/>
+    </row>
+    <row r="101" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A101" s="1"/>
+    </row>
+    <row r="102" spans="1:9" ht="13.5" customHeight="1">
       <c r="I102" s="1"/>
     </row>
-    <row r="103" ht="13.5" customHeight="1">
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
       <c r="I103" s="1"/>
     </row>
-    <row r="104" ht="13.5" customHeight="1">
+    <row r="104" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A104" s="1"/>
+      <c r="B104" s="1"/>
       <c r="I104" s="1"/>
     </row>
-    <row r="105" ht="13.5" customHeight="1">
+    <row r="105" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A105" s="1"/>
+      <c r="H105" s="1"/>
       <c r="I105" s="1"/>
     </row>
-    <row r="106" ht="13.5" customHeight="1">
+    <row r="106" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
       <c r="I106" s="1"/>
     </row>
-    <row r="107" ht="13.5" customHeight="1">
+    <row r="107" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B107" s="1"/>
+      <c r="C107" s="1"/>
       <c r="I107" s="1"/>
     </row>
-    <row r="108" ht="13.5" customHeight="1">
+    <row r="108" spans="1:9" ht="13.5" customHeight="1">
       <c r="B108" s="1"/>
       <c r="C108" s="1"/>
       <c r="I108" s="1"/>
     </row>
-    <row r="109" ht="13.5" customHeight="1">
-      <c r="B109" s="1"/>
-      <c r="C109" s="1"/>
+    <row r="109" spans="1:9" ht="13.5" customHeight="1">
       <c r="I109" s="1"/>
     </row>
-    <row r="110" ht="13.5" customHeight="1">
-      <c r="B110" s="1"/>
-      <c r="C110" s="1"/>
+    <row r="110" spans="1:9" ht="13.5" customHeight="1">
       <c r="I110" s="1"/>
     </row>
-    <row r="111" ht="13.5" customHeight="1">
-      <c r="B111" s="1"/>
-      <c r="C111" s="1"/>
+    <row r="111" spans="1:9" ht="13.5" customHeight="1">
       <c r="I111" s="1"/>
     </row>
-    <row r="112" ht="13.5" customHeight="1">
-      <c r="B112" s="1"/>
-      <c r="C112" s="1"/>
+    <row r="112" spans="1:9" ht="13.5" customHeight="1">
       <c r="I112" s="1"/>
     </row>
-    <row r="113" ht="13.5" customHeight="1">
-      <c r="A113" s="1"/>
+    <row r="113" spans="1:10" ht="13.5" customHeight="1">
       <c r="B113" s="1"/>
+      <c r="C113" s="1"/>
       <c r="I113" s="1"/>
-      <c r="J113" s="1"/>
-    </row>
-    <row r="114" ht="13.5" customHeight="1">
-      <c r="A114" s="1"/>
+    </row>
+    <row r="114" spans="1:10" ht="13.5" customHeight="1">
       <c r="B114" s="1"/>
+      <c r="C114" s="1"/>
       <c r="I114" s="1"/>
-      <c r="J114" s="1"/>
-    </row>
-    <row r="115" ht="13.5" customHeight="1">
-      <c r="A115" s="1"/>
+    </row>
+    <row r="115" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B115" s="1"/>
+      <c r="C115" s="1"/>
       <c r="I115" s="1"/>
-      <c r="J115" s="1"/>
-    </row>
-    <row r="116" ht="13.5" customHeight="1">
+    </row>
+    <row r="116" spans="1:10" ht="13.5" customHeight="1">
       <c r="B116" s="1"/>
       <c r="C116" s="1"/>
       <c r="I116" s="1"/>
     </row>
-    <row r="117" ht="13.5" customHeight="1">
-      <c r="A117" s="1"/>
+    <row r="117" spans="1:10" ht="13.5" customHeight="1">
       <c r="B117" s="1"/>
-    </row>
-    <row r="118" ht="13.5" customHeight="1">
+      <c r="C117" s="1"/>
+      <c r="I117" s="1"/>
+    </row>
+    <row r="118" spans="1:10" ht="13.5" customHeight="1">
       <c r="A118" s="1"/>
-    </row>
-    <row r="119" ht="13.5" customHeight="1">
+      <c r="B118" s="1"/>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1"/>
+    </row>
+    <row r="119" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A119" s="1"/>
       <c r="B119" s="1"/>
-      <c r="C119" s="1"/>
       <c r="I119" s="1"/>
-    </row>
-    <row r="120" ht="13.5" customHeight="1">
-      <c r="B120" s="1"/>
-      <c r="C120" s="1"/>
+      <c r="J119" s="1"/>
+    </row>
+    <row r="120" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A120" s="1"/>
       <c r="I120" s="1"/>
-    </row>
-    <row r="121" ht="13.5" customHeight="1">
+      <c r="J120" s="1"/>
+    </row>
+    <row r="121" spans="1:10" ht="13.5" customHeight="1">
       <c r="B121" s="1"/>
       <c r="C121" s="1"/>
       <c r="I121" s="1"/>
     </row>
-    <row r="122" ht="13.5" customHeight="1">
+    <row r="122" spans="1:10" ht="13.5" customHeight="1">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
     </row>
-    <row r="123" ht="13.5" customHeight="1">
+    <row r="123" spans="1:10" ht="13.5" customHeight="1">
       <c r="A123" s="1"/>
-      <c r="B123" s="1"/>
-      <c r="I123" s="1"/>
-      <c r="J123" s="1"/>
-    </row>
-    <row r="124" ht="13.5" customHeight="1">
+    </row>
+    <row r="124" spans="1:10" ht="13.5" customHeight="1">
       <c r="B124" s="1"/>
       <c r="C124" s="1"/>
       <c r="I124" s="1"/>
     </row>
-    <row r="125" ht="13.5" customHeight="1">
+    <row r="125" spans="1:10" ht="13.5" customHeight="1">
       <c r="B125" s="1"/>
       <c r="C125" s="1"/>
       <c r="I125" s="1"/>
     </row>
-    <row r="126" ht="13.5" customHeight="1">
-      <c r="A126" s="1"/>
+    <row r="126" spans="1:10" ht="13.5" customHeight="1">
       <c r="B126" s="1"/>
-    </row>
-    <row r="127" ht="13.5" customHeight="1">
+      <c r="C126" s="1"/>
+      <c r="I126" s="1"/>
+    </row>
+    <row r="127" spans="1:10" ht="13.5" customHeight="1">
       <c r="A127" s="1"/>
-    </row>
-    <row r="128" ht="13.5" customHeight="1">
+      <c r="B127" s="1"/>
+    </row>
+    <row r="128" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A128" s="1"/>
+      <c r="B128" s="1"/>
       <c r="I128" s="1"/>
-    </row>
-    <row r="129" ht="13.5" customHeight="1">
-      <c r="A129" s="1"/>
-    </row>
-    <row r="130" ht="13.5" customHeight="1">
-      <c r="A130" s="1"/>
-    </row>
-    <row r="131" ht="13.5" customHeight="1">
+      <c r="J128" s="1"/>
+    </row>
+    <row r="129" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B129" s="1"/>
+      <c r="C129" s="1"/>
+      <c r="I129" s="1"/>
+    </row>
+    <row r="130" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B130" s="1"/>
+      <c r="C130" s="1"/>
+      <c r="I130" s="1"/>
+    </row>
+    <row r="131" spans="1:9" ht="13.5" customHeight="1">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-    </row>
-    <row r="132" ht="13.5" customHeight="1">
+    </row>
+    <row r="132" spans="1:9" ht="13.5" customHeight="1">
       <c r="A132" s="1"/>
-      <c r="H132" s="1"/>
-      <c r="I132" s="1"/>
-    </row>
-    <row r="133" ht="13.5" customHeight="1">
+    </row>
+    <row r="133" spans="1:9" ht="13.5" customHeight="1">
       <c r="I133" s="1"/>
     </row>
-    <row r="134" ht="13.5" customHeight="1">
-      <c r="I134" s="1"/>
-    </row>
-    <row r="135" ht="13.5" customHeight="1">
-      <c r="I135" s="1"/>
-    </row>
-    <row r="136" ht="13.5" customHeight="1">
+    <row r="134" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A134" s="1"/>
+    </row>
+    <row r="135" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A135" s="1"/>
+    </row>
+    <row r="136" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A136" s="1"/>
+      <c r="B136" s="1"/>
+      <c r="H136" s="1"/>
       <c r="I136" s="1"/>
     </row>
-    <row r="137" ht="13.5" customHeight="1">
+    <row r="137" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A137" s="1"/>
+      <c r="H137" s="1"/>
       <c r="I137" s="1"/>
     </row>
-    <row r="138" ht="13.5" customHeight="1">
+    <row r="138" spans="1:9" ht="13.5" customHeight="1">
       <c r="I138" s="1"/>
     </row>
-    <row r="139" ht="13.5" customHeight="1">
+    <row r="139" spans="1:9" ht="13.5" customHeight="1">
       <c r="I139" s="1"/>
     </row>
-    <row r="140" ht="13.5" customHeight="1"/>
-    <row r="141" ht="13.5" customHeight="1"/>
-    <row r="142" ht="13.5" customHeight="1"/>
-    <row r="143" ht="13.5" customHeight="1"/>
-    <row r="144" ht="13.5" customHeight="1"/>
+    <row r="140" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I140" s="1"/>
+    </row>
+    <row r="141" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I141" s="1"/>
+    </row>
+    <row r="142" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I142" s="1"/>
+    </row>
+    <row r="143" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I143" s="1"/>
+    </row>
+    <row r="144" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I144" s="1"/>
+    </row>
     <row r="145" ht="13.5" customHeight="1"/>
     <row r="146" ht="13.5" customHeight="1"/>
     <row r="147" ht="13.5" customHeight="1"/>
@@ -1075,22 +1904,29 @@
     <row r="158" ht="13.5" customHeight="1"/>
     <row r="159" ht="13.5" customHeight="1"/>
     <row r="160" ht="13.5" customHeight="1"/>
-    <row r="161" ht="13.5" customHeight="1"/>
-    <row r="162" ht="13.5" customHeight="1"/>
-    <row r="163" ht="13.5" customHeight="1"/>
-    <row r="164" ht="13.5" customHeight="1"/>
-    <row r="165" ht="13.5" customHeight="1"/>
-    <row r="166" ht="13.5" customHeight="1"/>
-    <row r="167" ht="13.5" customHeight="1"/>
-    <row r="168" ht="13.5" customHeight="1"/>
-    <row r="169" ht="13.5" customHeight="1"/>
-    <row r="170" ht="13.5" customHeight="1"/>
-    <row r="171" ht="13.5" customHeight="1"/>
-    <row r="172" ht="13.5" customHeight="1"/>
-    <row r="173" ht="13.5" customHeight="1"/>
-    <row r="174" ht="13.5" customHeight="1"/>
-    <row r="175" ht="13.5" customHeight="1"/>
-    <row r="176" ht="13.5" customHeight="1"/>
+    <row r="161" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="162" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="163" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="164" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="165" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="166" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="167" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="168" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="169" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="170" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A170" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="171" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="172" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="173" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="174" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="175" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="176" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="177" ht="13.5" customHeight="1"/>
     <row r="178" ht="13.5" customHeight="1"/>
     <row r="179" ht="13.5" customHeight="1"/>
@@ -1973,10 +2809,14 @@
     <row r="1056" ht="13.5" customHeight="1"/>
     <row r="1057" ht="13.5" customHeight="1"/>
     <row r="1058" ht="13.5" customHeight="1"/>
+    <row r="1059" ht="13.5" customHeight="1"/>
+    <row r="1060" ht="13.5" customHeight="1"/>
+    <row r="1061" ht="13.5" customHeight="1"/>
+    <row r="1062" ht="13.5" customHeight="1"/>
+    <row r="1063" ht="13.5" customHeight="1"/>
   </sheetData>
-  <printOptions/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
+  <phoneticPr fontId="4"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/Assets/test260903/chapter0203.xlsx
+++ b/Assets/test260903/chapter0203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="197" documentId="11_E10EE94338F254052E83A027A8BF203497349031" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6F3E973B-4125-4B1F-9CB0-1DCDE6B50D1A}"/>
+  <xr:revisionPtr revIDLastSave="455" documentId="11_E10EE94338F254052E83A027A8BF203497349031" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6913C80-75CD-460A-85F8-575DE0C96AAD}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="181">
   <si>
     <t>Command</t>
   </si>
@@ -450,6 +450,370 @@
   <si>
     <t>でも、それだけじゃない。
 あのロシア人との会話では……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>FadeOut</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>（お前はガキを殺せって頼まれたから、
+殺そうとした、それだけってわけだ）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>キャラ左</t>
+    <rPh sb="3" eb="4">
+      <t>ヒダリ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>背景：街中</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>襲撃者</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>負傷</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>キャラ右</t>
+    <rPh sb="3" eb="4">
+      <t>ミギ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>（そんなクソ汚れを、
+野放しにしておくことはできるか？）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>（じゃあな）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>銃声（単発）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ぐぇっ……！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>&lt;Off&gt;</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>（受ける仕事は選ぶべきだったな。
+じゃないと、今日みたいに地雷を踏む</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>（子どもを子ども扱いしない輩が、
+アタシは世界で一番嫌いなんだよ）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>どうしたよ、エロガキ？
+また性の芽生え？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-8-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-8-b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あなたを信頼していいのか？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あなたが裏切る可能性は？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-8合流</t>
+    <rPh sb="10" eb="12">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>うーん、そうだね……
+100パー信頼しろとは言えないよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だって、この世に絶対はないし、
+誰だって裏切る可能性はあるからね</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アタシがアンタの期待通りに
+動かない可能性は全然あると思う</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でもさ、アタシはアタシを裏切らない</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>アタシ、ガキは嫌いなんだよね。基本</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>でも……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>照れ</t>
+    <rPh sb="0" eb="1">
+      <t>テ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>げっ！　
+エロガキ！　伏せろ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……！？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>white</t>
+  </si>
+  <si>
+    <t>爆発</t>
+  </si>
+  <si>
+    <t>x=10.</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>FadeIn</t>
+  </si>
+  <si>
+    <t>背景：黒</t>
+  </si>
+  <si>
+    <t>突如、少年の視界が光に包まれた</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>真っ白な光、次に轟音。
+そして全てを焦がす真っ赤な炎</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>自分たちが爆発に巻き込まれたと、
+少年が悟ったのは……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>横転した車から
+強引に引きずり出された時だった</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>はぁ、はぁ、今のは！？
+何が、何が起きたんだ！？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>背景：街中（車体爆発）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-9-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>何です！？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ロケットランチャーを撃ち込まれた！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だーーー！　ちくしょう！
+愛車が燃えるゴミになった！！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>どこのボケだーー！！
+ブッ殺してやるから出てこい！！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>美鈴……まだ生きているのか</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>白蛇の男</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>通常</t>
+    <rPh sb="0" eb="2">
+      <t>ツウジョウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>さっさと死ねばいいものを……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ん？　てめぇは……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-10-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>だ、誰なんです？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こいつは……
+アタシと同じ、白蛇の人間だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-11-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>えっ？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>こんにちは。
+君の叔父上から依頼を受けた者だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>残念だが、君には死んでもらう。
+これは白蛇全体の方針だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……今、何て言った？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>これは白蛇全体の意向だ。
+先ほど会議で決まったんだよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>末端構成員から、
+彼を殺す仕事が上がってきて……</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>幹部会で「請ける」と決定された。
+美鈴、君の護衛もここまでだ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>その子を渡せ。
+これは白蛇本体からの命令だ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>逆らえば、君は白蛇の敵になる</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>……はぁ、マジかよ</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>打死你（ダァスゥニィ）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>ぐおっ！？</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>女は襲撃者を撃った。
+そして少年の手を掴み、走り出した</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>走る足音</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>あははは！　上等上等！
+白蛇とケンカなんて最高じゃん！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>エロガキ！
+アタシも裏切られちゃった！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>これで裏切られ仲間だね、アタシたち！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-12-a</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-12-b</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>*選択肢0203-12合流</t>
+    <rPh sb="11" eb="13">
+      <t>ゴウリュウ</t>
+    </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>笑ってる場合ですか！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>どこ行くんですか！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>このままスラムに逃げる！
+で、武器を手に入れてカチコム！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>手を離すなよ！　エロガキ！</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>StopSe</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>炎が燃える音</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -520,7 +884,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -541,6 +905,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -760,7 +1130,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1063"/>
+  <dimension ref="A1:L1080"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -1605,344 +1975,1005 @@
       </c>
     </row>
     <row r="79" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B79" s="1"/>
-      <c r="C79" s="1"/>
+      <c r="A79" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G79">
+        <v>1</v>
+      </c>
       <c r="I79" s="1"/>
     </row>
     <row r="80" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B80" s="1"/>
-      <c r="C80" s="1"/>
+      <c r="A80" s="7"/>
+      <c r="B80" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C80" s="6" t="s">
+        <v>111</v>
+      </c>
       <c r="I80" s="1"/>
     </row>
     <row r="81" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B81" s="1"/>
-      <c r="C81" s="1"/>
+      <c r="A81" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B81" s="7" t="s">
+        <v>103</v>
+      </c>
       <c r="I81" s="1"/>
     </row>
     <row r="82" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B82" s="1"/>
-      <c r="C82" s="1"/>
+      <c r="A82" s="3"/>
+      <c r="B82" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C82" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>106</v>
+      </c>
       <c r="I82" s="1"/>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B83" s="1"/>
-      <c r="C83" s="1"/>
+      <c r="A83" s="3"/>
+      <c r="B83" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C83" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D83" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
     </row>
     <row r="84" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A84" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B84" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G84">
+        <v>1</v>
+      </c>
       <c r="I84" s="1"/>
     </row>
-    <row r="85" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I85" s="1"/>
-    </row>
-    <row r="86" spans="1:10" ht="13.5" customHeight="1">
-      <c r="I86" s="1"/>
-    </row>
-    <row r="87" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="I87" s="1"/>
+    <row r="85" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B85" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C85" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D85" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I85" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="86" spans="1:10" ht="27.6" customHeight="1">
+      <c r="B86" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C86" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D86" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I86" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J86" s="1"/>
+    </row>
+    <row r="87" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A87" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C87" s="6"/>
+      <c r="D87" s="6"/>
+      <c r="I87" s="5"/>
       <c r="J87" s="1"/>
     </row>
     <row r="88" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
+      <c r="B88" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C88" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D88" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I88" s="1" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="89" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A89" s="1"/>
+      <c r="B89" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C89" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I89" s="5" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B90" s="1"/>
-      <c r="C90" s="1"/>
+      <c r="B90" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>111</v>
+      </c>
       <c r="I90" s="1"/>
     </row>
-    <row r="91" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B91" s="1"/>
-      <c r="C91" s="1"/>
-      <c r="I91" s="1"/>
-    </row>
-    <row r="92" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="I92" s="1"/>
+    <row r="91" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A91" s="1"/>
+      <c r="B91" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="J91" s="1"/>
+    </row>
+    <row r="92" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A92" s="1"/>
+      <c r="B92" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C92" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D92" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I92" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="J92" s="1"/>
     </row>
     <row r="93" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="I93" s="1"/>
+      <c r="A93" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
     </row>
     <row r="94" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
+      <c r="A94" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I94" s="1"/>
     </row>
     <row r="95" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A95" s="1"/>
+      <c r="A95" s="3"/>
+      <c r="B95" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I95" s="1"/>
     </row>
     <row r="96" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
+      <c r="A96" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B96" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
       <c r="I96" s="1"/>
     </row>
     <row r="97" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B97" s="1"/>
+      <c r="B97" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="C97" s="1"/>
-      <c r="I97" s="1"/>
-    </row>
-    <row r="98" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B98" s="1"/>
-      <c r="C98" s="1"/>
-      <c r="I98" s="1"/>
+      <c r="I97" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="30" customHeight="1">
+      <c r="B98" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I98" s="5" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="99" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B99" s="1"/>
+      <c r="A99" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>116</v>
+      </c>
       <c r="C99" s="1"/>
-      <c r="I99" s="1"/>
+      <c r="I99" s="1" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="100" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A100" s="1"/>
-      <c r="B100" s="1"/>
+      <c r="A100" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I100" s="1" t="s">
+        <v>119</v>
+      </c>
     </row>
     <row r="101" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A101" s="1"/>
+      <c r="A101" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="102" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A102" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C102" s="1"/>
       <c r="I102" s="1"/>
     </row>
     <row r="103" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A103" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B103" s="1"/>
+      <c r="C103" s="1"/>
       <c r="I103" s="1"/>
     </row>
     <row r="104" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A104" s="1"/>
-      <c r="B104" s="1"/>
+      <c r="A104" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C104" s="1"/>
       <c r="I104" s="1"/>
     </row>
     <row r="105" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A105" s="1"/>
-      <c r="H105" s="1"/>
+      <c r="A105" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B105" s="1"/>
+      <c r="C105" s="1"/>
       <c r="I105" s="1"/>
     </row>
-    <row r="106" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
-      <c r="I106" s="1"/>
-    </row>
-    <row r="107" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B107" s="1"/>
-      <c r="C107" s="1"/>
-      <c r="I107" s="1"/>
-    </row>
-    <row r="108" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="I108" s="1"/>
+    <row r="106" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A106" s="1"/>
+      <c r="B106" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C106" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I106" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" ht="30" customHeight="1">
+      <c r="A107" s="1"/>
+      <c r="B107" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I107" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" ht="30" customHeight="1">
+      <c r="B108" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I108" s="5" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="109" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I109" s="1"/>
+      <c r="B109" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C109" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I109" s="5" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="110" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I110" s="1"/>
+      <c r="A110" s="1"/>
+      <c r="B110" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C110" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I110" s="5" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="111" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I111" s="1"/>
-    </row>
-    <row r="112" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I112" s="1"/>
-    </row>
-    <row r="113" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B113" s="1"/>
-      <c r="C113" s="1"/>
-      <c r="I113" s="1"/>
-    </row>
-    <row r="114" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
-      <c r="I114" s="1"/>
-    </row>
-    <row r="115" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
-      <c r="I115" s="1"/>
-    </row>
-    <row r="116" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="I116" s="1"/>
-    </row>
-    <row r="117" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B117" s="1"/>
+      <c r="A111" s="1"/>
+      <c r="B111" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H111" s="1"/>
+      <c r="I111" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B112" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A113" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B113" s="8" t="s">
+        <v>131</v>
+      </c>
+      <c r="C113" s="6"/>
+      <c r="I113" s="5"/>
+    </row>
+    <row r="114" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A114" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B114" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D114" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="I114" s="5"/>
+    </row>
+    <row r="115" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A115" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B115" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C115" s="6"/>
+      <c r="G115">
+        <v>1</v>
+      </c>
+      <c r="I115" s="5"/>
+    </row>
+    <row r="116" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A116" s="6"/>
+      <c r="B116" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I116" s="5"/>
+    </row>
+    <row r="117" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B117" s="7" t="s">
+        <v>33</v>
+      </c>
       <c r="C117" s="1"/>
-      <c r="I117" s="1"/>
-    </row>
-    <row r="118" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A118" s="1"/>
-      <c r="B118" s="1"/>
-      <c r="I118" s="1"/>
-      <c r="J118" s="1"/>
-    </row>
-    <row r="119" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A119" s="1"/>
-      <c r="B119" s="1"/>
+      <c r="I117" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A118" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C118" s="1"/>
+      <c r="I118" s="5"/>
+    </row>
+    <row r="119" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A119" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B119" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C119" s="1"/>
+      <c r="G119">
+        <v>1</v>
+      </c>
       <c r="I119" s="1"/>
-      <c r="J119" s="1"/>
-    </row>
-    <row r="120" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A120" s="1"/>
-      <c r="I120" s="1"/>
-      <c r="J120" s="1"/>
-    </row>
-    <row r="121" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B121" s="1"/>
-      <c r="C121" s="1"/>
-      <c r="I121" s="1"/>
-    </row>
-    <row r="122" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
-    </row>
-    <row r="123" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A123" s="1"/>
-    </row>
-    <row r="124" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B124" s="1"/>
-      <c r="C124" s="1"/>
-      <c r="I124" s="1"/>
-    </row>
-    <row r="125" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B125" s="1"/>
-      <c r="C125" s="1"/>
-      <c r="I125" s="1"/>
-    </row>
-    <row r="126" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B126" s="1"/>
-      <c r="C126" s="1"/>
-      <c r="I126" s="1"/>
-    </row>
-    <row r="127" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A127" s="1"/>
-      <c r="B127" s="1"/>
-    </row>
-    <row r="128" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A128" s="1"/>
-      <c r="B128" s="1"/>
-      <c r="I128" s="1"/>
-      <c r="J128" s="1"/>
-    </row>
-    <row r="129" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B129" s="1"/>
+    </row>
+    <row r="120" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I120" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9" ht="27.6" customHeight="1">
+      <c r="I121" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="27.6" customHeight="1">
+      <c r="A122" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G122">
+        <v>1</v>
+      </c>
+      <c r="I122" s="5"/>
+    </row>
+    <row r="123" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I123" s="5" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="124" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A124" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="I124" s="5"/>
+    </row>
+    <row r="125" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A125" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G125">
+        <v>1</v>
+      </c>
+      <c r="I125" s="5"/>
+    </row>
+    <row r="126" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A126" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="I126" s="5"/>
+    </row>
+    <row r="127" spans="1:9" ht="30.6" customHeight="1">
+      <c r="I127" s="5" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="128" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B128" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I128" s="5" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="129" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A129" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="C129" s="1"/>
-      <c r="I129" s="1"/>
-    </row>
-    <row r="130" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I129" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="130" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A130" s="1" t="s">
+        <v>141</v>
+      </c>
       <c r="B130" s="1"/>
       <c r="C130" s="1"/>
       <c r="I130" s="1"/>
     </row>
-    <row r="131" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
-    </row>
-    <row r="132" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A132" s="1"/>
-    </row>
-    <row r="133" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I133" s="1"/>
-    </row>
-    <row r="134" spans="1:9" ht="13.5" customHeight="1">
+    <row r="131" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B131" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C131" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I131" s="5" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="132" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B132" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C132" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I132" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="133" spans="1:10" ht="30" customHeight="1">
+      <c r="A133" s="1"/>
+      <c r="B133" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C133" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I133" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="J133" s="1"/>
+    </row>
+    <row r="134" spans="1:10" ht="13.5" customHeight="1">
       <c r="A134" s="1"/>
-    </row>
-    <row r="135" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B134" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C134" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I134" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J134" s="1"/>
+    </row>
+    <row r="135" spans="1:10" ht="13.5" customHeight="1">
       <c r="A135" s="1"/>
-    </row>
-    <row r="136" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A136" s="1"/>
-      <c r="B136" s="1"/>
-      <c r="H136" s="1"/>
-      <c r="I136" s="1"/>
-    </row>
-    <row r="137" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A137" s="1"/>
-      <c r="H137" s="1"/>
-      <c r="I137" s="1"/>
-    </row>
-    <row r="138" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I138" s="1"/>
-    </row>
-    <row r="139" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I139" s="1"/>
-    </row>
-    <row r="140" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I140" s="1"/>
-    </row>
-    <row r="141" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B135" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C135" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I135" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="J135" s="1"/>
+    </row>
+    <row r="136" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B136" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C136" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I136" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A137" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I137" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="138" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A138" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="139" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B139" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I139" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="140" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A140" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C140" s="1"/>
+      <c r="I140" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="141" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A141" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B141" s="1"/>
+      <c r="C141" s="1"/>
       <c r="I141" s="1"/>
     </row>
-    <row r="142" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I142" s="1"/>
-    </row>
-    <row r="143" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I143" s="1"/>
-    </row>
-    <row r="144" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I144" s="1"/>
-    </row>
-    <row r="145" ht="13.5" customHeight="1"/>
-    <row r="146" ht="13.5" customHeight="1"/>
-    <row r="147" ht="13.5" customHeight="1"/>
-    <row r="148" ht="13.5" customHeight="1"/>
-    <row r="149" ht="13.5" customHeight="1"/>
-    <row r="150" ht="13.5" customHeight="1"/>
-    <row r="151" ht="13.5" customHeight="1"/>
-    <row r="152" ht="13.5" customHeight="1"/>
-    <row r="153" ht="13.5" customHeight="1"/>
-    <row r="154" ht="13.5" customHeight="1"/>
-    <row r="155" ht="13.5" customHeight="1"/>
-    <row r="156" ht="13.5" customHeight="1"/>
-    <row r="157" ht="13.5" customHeight="1"/>
-    <row r="158" ht="13.5" customHeight="1"/>
-    <row r="159" ht="13.5" customHeight="1"/>
-    <row r="160" ht="13.5" customHeight="1"/>
-    <row r="161" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="162" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="163" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="164" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="165" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="166" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="167" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="168" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="169" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="170" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A170" s="1" t="s">
+    <row r="142" spans="1:10" ht="30" customHeight="1">
+      <c r="A142" s="1"/>
+      <c r="B142" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C142" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I142" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="143" spans="1:10" ht="30.6" customHeight="1">
+      <c r="A143" s="1"/>
+      <c r="B143" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C143" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I143" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J143" s="1"/>
+    </row>
+    <row r="144" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B144" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C144" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I144" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="145" spans="1:9" ht="30" customHeight="1">
+      <c r="B145" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I145" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="146" spans="1:9" ht="31.2" customHeight="1">
+      <c r="A146" s="1"/>
+      <c r="B146" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C146" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I146" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="147" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A147" s="1"/>
+      <c r="B147" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C147" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I147" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="148" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B148" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C148" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I148" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="149" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A149" s="1"/>
+      <c r="B149" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C149" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I149" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="150" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A150" s="1"/>
+      <c r="B150" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C150" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I150" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="151" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A151" s="1"/>
+      <c r="B151" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C151" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H151" s="1"/>
+      <c r="I151" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="152" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A152" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B152" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C152" s="6"/>
+      <c r="H152" s="1"/>
+      <c r="I152" s="5"/>
+    </row>
+    <row r="153" spans="1:9" ht="13.2" customHeight="1">
+      <c r="A153" s="1"/>
+      <c r="B153" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C153" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H153" s="1"/>
+      <c r="I153" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="154" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B154" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I154" s="1"/>
+    </row>
+    <row r="155" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A155" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B155" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C155" s="6"/>
+      <c r="I155" s="1"/>
+    </row>
+    <row r="156" spans="1:9" ht="30.6" customHeight="1">
+      <c r="I156" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B157" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I157" s="5" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B158" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C158" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I158" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="159" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B159" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I159" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="160" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A160" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I160" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A161" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I161" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A162" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A163" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="164" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A164" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A165" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="166" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A166" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B167" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C167" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I167" s="10" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="168" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B168" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C168" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I168" s="9" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A169" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B169" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A170" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B170" s="9" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B171" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C171" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="173" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="174" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="175" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="176" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="177" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="178" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="179" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="180" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="181" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="182" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="183" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="184" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="185" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="186" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="187" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A187" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B170" s="1" t="s">
+      <c r="B187" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="171" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="172" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="173" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="174" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="175" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="176" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="177" ht="13.5" customHeight="1"/>
-    <row r="178" ht="13.5" customHeight="1"/>
-    <row r="179" ht="13.5" customHeight="1"/>
-    <row r="180" ht="13.5" customHeight="1"/>
-    <row r="181" ht="13.5" customHeight="1"/>
-    <row r="182" ht="13.5" customHeight="1"/>
-    <row r="183" ht="13.5" customHeight="1"/>
-    <row r="184" ht="13.5" customHeight="1"/>
-    <row r="185" ht="13.5" customHeight="1"/>
-    <row r="186" ht="13.5" customHeight="1"/>
-    <row r="187" ht="13.5" customHeight="1"/>
-    <row r="188" ht="13.5" customHeight="1"/>
-    <row r="189" ht="13.5" customHeight="1"/>
-    <row r="190" ht="13.5" customHeight="1"/>
-    <row r="191" ht="13.5" customHeight="1"/>
-    <row r="192" ht="13.5" customHeight="1"/>
+    <row r="188" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="189" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="190" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="191" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="192" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="193" ht="13.5" customHeight="1"/>
     <row r="194" ht="13.5" customHeight="1"/>
     <row r="195" ht="13.5" customHeight="1"/>
@@ -2814,6 +3845,23 @@
     <row r="1061" ht="13.5" customHeight="1"/>
     <row r="1062" ht="13.5" customHeight="1"/>
     <row r="1063" ht="13.5" customHeight="1"/>
+    <row r="1064" ht="13.5" customHeight="1"/>
+    <row r="1065" ht="13.5" customHeight="1"/>
+    <row r="1066" ht="13.5" customHeight="1"/>
+    <row r="1067" ht="13.5" customHeight="1"/>
+    <row r="1068" ht="13.5" customHeight="1"/>
+    <row r="1069" ht="13.5" customHeight="1"/>
+    <row r="1070" ht="13.5" customHeight="1"/>
+    <row r="1071" ht="13.5" customHeight="1"/>
+    <row r="1072" ht="13.5" customHeight="1"/>
+    <row r="1073" ht="13.5" customHeight="1"/>
+    <row r="1074" ht="13.5" customHeight="1"/>
+    <row r="1075" ht="13.5" customHeight="1"/>
+    <row r="1076" ht="13.5" customHeight="1"/>
+    <row r="1077" ht="13.5" customHeight="1"/>
+    <row r="1078" ht="13.5" customHeight="1"/>
+    <row r="1079" ht="13.5" customHeight="1"/>
+    <row r="1080" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Assets/test260903/chapter0203.xlsx
+++ b/Assets/test260903/chapter0203.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="455" documentId="11_E10EE94338F254052E83A027A8BF203497349031" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6913C80-75CD-460A-85F8-575DE0C96AAD}"/>
+  <xr:revisionPtr revIDLastSave="474" documentId="11_E10EE94338F254052E83A027A8BF203497349031" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D90E1CF4-E628-449F-B7F6-C8AEFE0BD8B7}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="183">
   <si>
     <t>Command</t>
   </si>
@@ -814,6 +814,18 @@
   </si>
   <si>
     <t>炎が燃える音</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>（つまり、お前は命令さえあれば、
+ガキでも殺す男なんだな？）</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>キャラ中央</t>
+    <rPh sb="3" eb="5">
+      <t>チュウオウ</t>
+    </rPh>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1130,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1080"/>
+  <dimension ref="A1:L1084"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -1254,6 +1266,9 @@
       <c r="B8" s="1" t="s">
         <v>24</v>
       </c>
+      <c r="C8" s="9" t="b">
+        <v>1</v>
+      </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
       <c r="K8" s="1"/>
@@ -1974,90 +1989,86 @@
         <v>99</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A79" s="7" t="s">
+    <row r="79" spans="1:9" ht="28.2" customHeight="1">
+      <c r="A79" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B79" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="I79" s="5"/>
+    </row>
+    <row r="80" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A80" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B80" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G79">
+      <c r="G80">
         <v>1</v>
       </c>
-      <c r="I79" s="1"/>
-    </row>
-    <row r="80" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A80" s="7"/>
-      <c r="B80" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C80" s="6" t="s">
+      <c r="I80" s="1"/>
+    </row>
+    <row r="81" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A81" s="7"/>
+      <c r="B81" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C81" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="I80" s="1"/>
-    </row>
-    <row r="81" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A81" s="3" t="s">
+      <c r="I81" s="1"/>
+    </row>
+    <row r="82" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A82" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B81" s="7" t="s">
+      <c r="B82" s="7" t="s">
         <v>103</v>
-      </c>
-      <c r="I81" s="1"/>
-    </row>
-    <row r="82" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A82" s="3"/>
-      <c r="B82" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C82" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D82" s="9" t="s">
-        <v>106</v>
       </c>
       <c r="I82" s="1"/>
     </row>
     <row r="83" spans="1:10" ht="13.5" customHeight="1">
       <c r="A83" s="3"/>
       <c r="B83" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C83" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I83" s="1"/>
+    </row>
+    <row r="84" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A84" s="3"/>
+      <c r="B84" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="D84" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I83" s="1"/>
-    </row>
-    <row r="84" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A84" s="6" t="s">
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A85" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B84" s="7" t="s">
+      <c r="B85" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G84">
+      <c r="G85">
         <v>1</v>
       </c>
-      <c r="I84" s="1"/>
-    </row>
-    <row r="85" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B85" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C85" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D85" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I85" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="86" spans="1:10" ht="27.6" customHeight="1">
+      <c r="I85" s="1"/>
+    </row>
+    <row r="86" spans="1:10" ht="28.2" customHeight="1">
       <c r="B86" s="6" t="s">
         <v>31</v>
       </c>
@@ -2068,23 +2079,24 @@
         <v>102</v>
       </c>
       <c r="I86" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="J86" s="1"/>
-    </row>
-    <row r="87" spans="1:10" ht="27.6" customHeight="1">
-      <c r="A87" s="8" t="s">
-        <v>23</v>
-      </c>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" ht="28.2" customHeight="1">
       <c r="B87" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C87" s="6"/>
-      <c r="D87" s="6"/>
-      <c r="I87" s="5"/>
-      <c r="J87" s="1"/>
-    </row>
-    <row r="88" spans="1:10" ht="13.5" customHeight="1">
+        <v>31</v>
+      </c>
+      <c r="C87" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D87" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I87" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="88" spans="1:10" ht="27.6" customHeight="1">
       <c r="B88" s="6" t="s">
         <v>31</v>
       </c>
@@ -2094,238 +2106,243 @@
       <c r="D88" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I88" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="89" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I88" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="J88" s="1"/>
+    </row>
+    <row r="89" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A89" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="B89" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C89" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D89" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="I89" s="5" t="s">
-        <v>110</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="C89" s="6"/>
+      <c r="D89" s="6"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="1"/>
     </row>
     <row r="90" spans="1:10" ht="13.5" customHeight="1">
       <c r="B90" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C90" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D90" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I90" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B91" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C90" s="6" t="s">
+      <c r="C91" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I91" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B92" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C92" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="I90" s="1"/>
-    </row>
-    <row r="91" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A91" s="1"/>
-      <c r="B91" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C91" s="6" t="s">
+      <c r="I92" s="1"/>
+    </row>
+    <row r="93" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A93" s="1"/>
+      <c r="B93" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C93" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D91" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I91" s="5" t="s">
+      <c r="D93" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="I93" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="J91" s="1"/>
-    </row>
-    <row r="92" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A92" s="1"/>
-      <c r="B92" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C92" s="6" t="s">
+      <c r="J93" s="1"/>
+    </row>
+    <row r="94" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A94" s="1"/>
+      <c r="B94" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C94" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D92" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I92" s="5" t="s">
+      <c r="D94" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="I94" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="J92" s="1"/>
-    </row>
-    <row r="93" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A93" s="7" t="s">
+      <c r="J94" s="1"/>
+    </row>
+    <row r="95" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A95" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B93" s="7" t="s">
+      <c r="B95" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G93">
+      <c r="G95">
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A94" s="3" t="s">
+    <row r="96" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A96" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B94" s="7" t="s">
+      <c r="B96" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="I94" s="1"/>
-    </row>
-    <row r="95" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A95" s="3"/>
-      <c r="B95" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C95" s="6" t="s">
+      <c r="I96" s="1"/>
+    </row>
+    <row r="97" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A97" s="3"/>
+      <c r="B97" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C97" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="I95" s="1"/>
-    </row>
-    <row r="96" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A96" s="6" t="s">
+      <c r="I97" s="1"/>
+    </row>
+    <row r="98" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A98" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B96" s="7" t="s">
+      <c r="B98" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G96">
+      <c r="G98">
         <v>1</v>
       </c>
-      <c r="I96" s="1"/>
-    </row>
-    <row r="97" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B97" s="7" t="s">
+      <c r="I98" s="1"/>
+    </row>
+    <row r="99" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A99" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C99" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I99" s="1"/>
+    </row>
+    <row r="100" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B100" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C97" s="1"/>
-      <c r="I97" s="1" t="s">
+      <c r="C100" s="1"/>
+      <c r="I100" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="98" spans="1:9" ht="30" customHeight="1">
-      <c r="B98" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C98" s="7" t="s">
+    <row r="101" spans="1:9" ht="30" customHeight="1">
+      <c r="B101" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C101" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I98" s="5" t="s">
+      <c r="I101" s="5" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="99" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A99" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B99" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C99" s="1"/>
-      <c r="I99" s="1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="100" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A100" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B100" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I100" s="1" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A101" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="102" spans="1:9" ht="13.5" customHeight="1">
       <c r="A102" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="C102" s="1"/>
+      <c r="I102" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A103" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="I103" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A104" s="1" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A105" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B105" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C102" s="1"/>
-      <c r="I102" s="1"/>
-    </row>
-    <row r="103" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A103" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="B103" s="1"/>
-      <c r="C103" s="1"/>
-      <c r="I103" s="1"/>
-    </row>
-    <row r="104" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A104" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B104" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="C104" s="1"/>
-      <c r="I104" s="1"/>
-    </row>
-    <row r="105" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A105" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B105" s="1"/>
       <c r="C105" s="1"/>
       <c r="I105" s="1"/>
     </row>
-    <row r="106" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A106" s="1"/>
-      <c r="B106" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C106" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I106" s="10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="107" spans="1:9" ht="30" customHeight="1">
-      <c r="A107" s="1"/>
-      <c r="B107" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I107" s="10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="108" spans="1:9" ht="30" customHeight="1">
-      <c r="B108" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I108" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9" ht="13.5" customHeight="1">
+    <row r="106" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A106" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="B106" s="1"/>
+      <c r="C106" s="1"/>
+      <c r="I106" s="1"/>
+    </row>
+    <row r="107" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A107" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C107" s="1"/>
+      <c r="I107" s="1"/>
+    </row>
+    <row r="108" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A108" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B108" s="1"/>
+      <c r="C108" s="1"/>
+      <c r="I108" s="1"/>
+    </row>
+    <row r="109" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A109" s="1"/>
       <c r="B109" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C109" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I109" s="5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I109" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" ht="30" customHeight="1">
       <c r="A110" s="1"/>
       <c r="B110" s="6" t="s">
         <v>31</v>
@@ -2333,263 +2350,260 @@
       <c r="C110" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I110" s="5" t="s">
+      <c r="I110" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" ht="30" customHeight="1">
+      <c r="B111" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C111" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I111" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B112" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C112" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A113" s="1"/>
+      <c r="B113" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C113" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I113" s="5" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="111" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A111" s="1"/>
-      <c r="B111" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C111" s="6" t="s">
+    <row r="114" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A114" s="1"/>
+      <c r="B114" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C114" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="H111" s="1"/>
-      <c r="I111" s="5" t="s">
+      <c r="H114" s="1"/>
+      <c r="I114" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="112" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B112" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C112" s="6" t="s">
+    <row r="115" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B115" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C115" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I112" s="5" t="s">
+      <c r="I115" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="113" spans="1:9" ht="30.6" customHeight="1">
-      <c r="A113" s="8" t="s">
+    <row r="116" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A116" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C116" s="6"/>
+      <c r="I116" s="5"/>
+    </row>
+    <row r="117" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A117" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B113" s="8" t="s">
+      <c r="B117" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C113" s="6"/>
-      <c r="I113" s="5"/>
-    </row>
-    <row r="114" spans="1:9" ht="30.6" customHeight="1">
-      <c r="A114" s="6" t="s">
+      <c r="C117" s="6"/>
+      <c r="I117" s="5"/>
+    </row>
+    <row r="118" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A118" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B114" s="7" t="s">
+      <c r="B118" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D114" s="6" t="s">
+      <c r="D118" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="I114" s="5"/>
-    </row>
-    <row r="115" spans="1:9" ht="30.6" customHeight="1">
-      <c r="A115" s="6" t="s">
+      <c r="I118" s="5"/>
+    </row>
+    <row r="119" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A119" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="B115" s="6" t="s">
-        <v>130</v>
-      </c>
-      <c r="C115" s="6"/>
-      <c r="G115">
-        <v>1</v>
-      </c>
-      <c r="I115" s="5"/>
-    </row>
-    <row r="116" spans="1:9" ht="30.6" customHeight="1">
-      <c r="A116" s="6"/>
-      <c r="B116" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C116" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="I116" s="5"/>
-    </row>
-    <row r="117" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B117" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C117" s="1"/>
-      <c r="I117" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="118" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A118" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C118" s="1"/>
-      <c r="I118" s="5"/>
-    </row>
-    <row r="119" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A119" s="9" t="s">
-        <v>133</v>
       </c>
       <c r="B119" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C119" s="1"/>
+      <c r="C119" s="6"/>
       <c r="G119">
         <v>1</v>
       </c>
-      <c r="I119" s="1"/>
-    </row>
-    <row r="120" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I120" s="1" t="s">
+      <c r="I119" s="5"/>
+    </row>
+    <row r="120" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A120" s="6"/>
+      <c r="B120" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C120" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I120" s="5"/>
+    </row>
+    <row r="121" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B121" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C121" s="1"/>
+      <c r="I121" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="122" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A122" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="C122" s="1"/>
+      <c r="I122" s="5"/>
+    </row>
+    <row r="123" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A123" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="B123" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="C123" s="1"/>
+      <c r="G123">
+        <v>1</v>
+      </c>
+      <c r="I123" s="1"/>
+    </row>
+    <row r="124" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I124" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="121" spans="1:9" ht="27.6" customHeight="1">
-      <c r="I121" s="5" t="s">
+    <row r="125" spans="1:9" ht="27.6" customHeight="1">
+      <c r="I125" s="5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="27.6" customHeight="1">
-      <c r="A122" s="7" t="s">
+    <row r="126" spans="1:9" ht="27.6" customHeight="1">
+      <c r="A126" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B122" s="7" t="s">
+      <c r="B126" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G122">
+      <c r="G126">
         <v>1</v>
       </c>
-      <c r="I122" s="5"/>
-    </row>
-    <row r="123" spans="1:9" ht="28.8" customHeight="1">
-      <c r="I123" s="5" t="s">
+      <c r="I126" s="5"/>
+    </row>
+    <row r="127" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I127" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="124" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A124" s="11" t="s">
+    <row r="128" spans="1:9" ht="28.8" customHeight="1">
+      <c r="A128" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B124" s="7" t="s">
+      <c r="B128" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="I124" s="5"/>
-    </row>
-    <row r="125" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A125" s="6" t="s">
+      <c r="I128" s="5"/>
+    </row>
+    <row r="129" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A129" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B125" s="7" t="s">
+      <c r="B129" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G125">
+      <c r="G129">
         <v>1</v>
       </c>
-      <c r="I125" s="5"/>
-    </row>
-    <row r="126" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A126" s="8" t="s">
+      <c r="I129" s="5"/>
+    </row>
+    <row r="130" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A130" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B126" s="7" t="s">
+      <c r="B130" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="I126" s="5"/>
-    </row>
-    <row r="127" spans="1:9" ht="30.6" customHeight="1">
-      <c r="I127" s="5" t="s">
+      <c r="C130" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I130" s="5"/>
+    </row>
+    <row r="131" spans="1:10" ht="30.6" customHeight="1">
+      <c r="I131" s="5" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B128" s="7" t="s">
+    <row r="132" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B132" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I128" s="5" t="s">
+      <c r="I132" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="129" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A129" s="9" t="s">
+    <row r="133" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A133" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B129" s="1" t="s">
+      <c r="B133" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C129" s="1"/>
-      <c r="I129" s="1" t="s">
+      <c r="C133" s="1"/>
+      <c r="I133" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="130" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A130" s="1" t="s">
+    <row r="134" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A134" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B130" s="1"/>
-      <c r="C130" s="1"/>
-      <c r="I130" s="1"/>
-    </row>
-    <row r="131" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B131" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C131" s="6" t="s">
+      <c r="B134" s="1"/>
+      <c r="C134" s="1"/>
+      <c r="I134" s="1"/>
+    </row>
+    <row r="135" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B135" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C135" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I131" s="5" t="s">
+      <c r="I135" s="5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B132" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C132" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I132" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="133" spans="1:10" ht="30" customHeight="1">
-      <c r="A133" s="1"/>
-      <c r="B133" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C133" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I133" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="J133" s="1"/>
-    </row>
-    <row r="134" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A134" s="1"/>
-      <c r="B134" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C134" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="I134" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J134" s="1"/>
-    </row>
-    <row r="135" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A135" s="1"/>
-      <c r="B135" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C135" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="I135" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="J135" s="1"/>
-    </row>
-    <row r="136" spans="1:10" ht="13.5" customHeight="1">
+    <row r="136" spans="1:10" ht="28.8" customHeight="1">
       <c r="B136" s="6" t="s">
         <v>31</v>
       </c>
@@ -2597,104 +2611,107 @@
         <v>47</v>
       </c>
       <c r="I136" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="137" spans="1:10" ht="30" customHeight="1">
+      <c r="A137" s="1"/>
+      <c r="B137" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C137" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I137" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="J137" s="1"/>
+    </row>
+    <row r="138" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A138" s="1"/>
+      <c r="B138" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C138" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I138" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J138" s="1"/>
+    </row>
+    <row r="139" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A139" s="1"/>
+      <c r="B139" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C139" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I139" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="J139" s="1"/>
+    </row>
+    <row r="140" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B140" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C140" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="I140" s="5" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A137" s="9" t="s">
+    <row r="141" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A141" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B137" s="1" t="s">
+      <c r="B141" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="I137" s="5" t="s">
+      <c r="I141" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="138" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A138" s="1" t="s">
+    <row r="142" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A142" s="1" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="139" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B139" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C139" s="6" t="s">
+    <row r="143" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B143" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C143" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I139" s="5" t="s">
+      <c r="I143" s="5" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="140" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A140" s="9" t="s">
+    <row r="144" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A144" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B140" s="1" t="s">
+      <c r="B144" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="C140" s="1"/>
-      <c r="I140" s="5" t="s">
+      <c r="C144" s="1"/>
+      <c r="I144" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="141" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A141" s="1" t="s">
+    <row r="145" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A145" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B141" s="1"/>
-      <c r="C141" s="1"/>
-      <c r="I141" s="1"/>
-    </row>
-    <row r="142" spans="1:10" ht="30" customHeight="1">
-      <c r="A142" s="1"/>
-      <c r="B142" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C142" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="I142" s="10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A143" s="1"/>
-      <c r="B143" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C143" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="I143" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="J143" s="1"/>
-    </row>
-    <row r="144" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B144" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C144" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I144" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="145" spans="1:9" ht="30" customHeight="1">
-      <c r="B145" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C145" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="I145" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="146" spans="1:9" ht="31.2" customHeight="1">
+      <c r="B145" s="1"/>
+      <c r="C145" s="1"/>
+      <c r="I145" s="1"/>
+    </row>
+    <row r="146" spans="1:10" ht="30" customHeight="1">
       <c r="A146" s="1"/>
       <c r="B146" s="6" t="s">
         <v>147</v>
@@ -2703,10 +2720,10 @@
         <v>148</v>
       </c>
       <c r="I146" s="10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="147" spans="1:9" ht="28.2" customHeight="1">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="147" spans="1:10" ht="30.6" customHeight="1">
       <c r="A147" s="1"/>
       <c r="B147" s="6" t="s">
         <v>147</v>
@@ -2714,23 +2731,23 @@
       <c r="C147" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="I147" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="148" spans="1:9" ht="28.8" customHeight="1">
+      <c r="I147" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="J147" s="1"/>
+    </row>
+    <row r="148" spans="1:10" ht="13.5" customHeight="1">
       <c r="B148" s="6" t="s">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="I148" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="149" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A149" s="1"/>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="30" customHeight="1">
       <c r="B149" s="6" t="s">
         <v>147</v>
       </c>
@@ -2738,46 +2755,45 @@
         <v>148</v>
       </c>
       <c r="I149" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="150" spans="1:9" ht="13.5" customHeight="1">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="31.2" customHeight="1">
       <c r="A150" s="1"/>
       <c r="B150" s="6" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="I150" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="151" spans="1:9" ht="13.5" customHeight="1">
+        <v>148</v>
+      </c>
+      <c r="I150" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="28.2" customHeight="1">
       <c r="A151" s="1"/>
       <c r="B151" s="6" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="H151" s="1"/>
-      <c r="I151" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="152" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A152" s="8" t="s">
-        <v>23</v>
-      </c>
+        <v>148</v>
+      </c>
+      <c r="I151" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="28.8" customHeight="1">
       <c r="B152" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C152" s="6"/>
-      <c r="H152" s="1"/>
-      <c r="I152" s="5"/>
-    </row>
-    <row r="153" spans="1:9" ht="13.2" customHeight="1">
+        <v>147</v>
+      </c>
+      <c r="C152" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I152" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="153" spans="1:10" ht="13.5" customHeight="1">
       <c r="A153" s="1"/>
       <c r="B153" s="6" t="s">
         <v>147</v>
@@ -2785,172 +2801,226 @@
       <c r="C153" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="H153" s="1"/>
       <c r="I153" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A154" s="1"/>
+      <c r="B154" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C154" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I154" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="155" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A155" s="1"/>
+      <c r="B155" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C155" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H155" s="1"/>
+      <c r="I155" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A156" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B156" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C156" s="6"/>
+      <c r="H156" s="1"/>
+      <c r="I156" s="5"/>
+    </row>
+    <row r="157" spans="1:10" ht="13.2" customHeight="1">
+      <c r="A157" s="1"/>
+      <c r="B157" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C157" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H157" s="1"/>
+      <c r="I157" s="5" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="154" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B154" s="6" t="s">
+    <row r="158" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B158" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="C154" s="6" t="s">
+      <c r="C158" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="I154" s="1"/>
-    </row>
-    <row r="155" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A155" s="8" t="s">
+      <c r="I158" s="1"/>
+    </row>
+    <row r="159" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A159" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B155" s="6" t="s">
+      <c r="B159" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C155" s="6"/>
-      <c r="I155" s="1"/>
-    </row>
-    <row r="156" spans="1:9" ht="30.6" customHeight="1">
-      <c r="I156" s="5" t="s">
+      <c r="C159" s="6"/>
+      <c r="I159" s="1"/>
+    </row>
+    <row r="160" spans="1:10" ht="30.6" customHeight="1">
+      <c r="I160" s="5" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="157" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B157" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C157" s="6" t="s">
+    <row r="161" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B161" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C161" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I157" s="5" t="s">
+      <c r="I161" s="5" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="158" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B158" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C158" s="6" t="s">
+    <row r="162" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B162" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C162" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I158" s="5" t="s">
+      <c r="I162" s="5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="159" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B159" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C159" s="6" t="s">
+    <row r="163" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B163" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C163" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I159" s="5" t="s">
+      <c r="I163" s="5" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="160" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A160" s="9" t="s">
+    <row r="164" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A164" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B160" s="1" t="s">
+      <c r="B164" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="I160" s="5" t="s">
+      <c r="I164" s="5" t="s">
         <v>175</v>
-      </c>
-    </row>
-    <row r="161" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A161" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B161" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="I161" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="162" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A162" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="163" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A163" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B163" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A164" s="1" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="165" spans="1:9" ht="13.5" customHeight="1">
       <c r="A165" s="9" t="s">
-        <v>86</v>
+        <v>48</v>
       </c>
       <c r="B165" s="1" t="s">
-        <v>174</v>
+        <v>173</v>
+      </c>
+      <c r="I165" s="5" t="s">
+        <v>176</v>
       </c>
     </row>
     <row r="166" spans="1:9" ht="13.5" customHeight="1">
       <c r="A166" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="167" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A167" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B167" s="1" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="167" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B167" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C167" s="6" t="s">
+    <row r="168" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A168" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="169" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A169" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A170" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B171" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C171" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I167" s="10" t="s">
+      <c r="I171" s="10" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="168" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B168" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C168" s="6" t="s">
+    <row r="172" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B172" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C172" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I168" s="9" t="s">
+      <c r="I172" s="9" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="169" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A169" s="6" t="s">
+    <row r="173" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A173" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B169" s="6" t="s">
+      <c r="B173" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="170" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A170" s="6" t="s">
+    <row r="174" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A174" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B170" s="9" t="s">
+      <c r="B174" s="9" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="171" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B171" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C171" s="6" t="s">
+    <row r="175" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B175" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C175" s="6" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="173" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="174" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="175" spans="1:9" ht="13.5" customHeight="1"/>
-    <row r="176" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="176" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A176" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="B176" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G176">
+        <v>1</v>
+      </c>
+    </row>
     <row r="177" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="178" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="179" spans="1:2" ht="13.5" customHeight="1"/>
@@ -2961,18 +3031,18 @@
     <row r="184" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="185" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="186" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="187" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A187" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B187" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
+    <row r="187" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="188" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="189" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="190" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="191" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="191" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A191" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="192" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="193" ht="13.5" customHeight="1"/>
     <row r="194" ht="13.5" customHeight="1"/>
@@ -3862,6 +3932,10 @@
     <row r="1078" ht="13.5" customHeight="1"/>
     <row r="1079" ht="13.5" customHeight="1"/>
     <row r="1080" ht="13.5" customHeight="1"/>
+    <row r="1081" ht="13.5" customHeight="1"/>
+    <row r="1082" ht="13.5" customHeight="1"/>
+    <row r="1083" ht="13.5" customHeight="1"/>
+    <row r="1084" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>

--- a/Assets/test260903/chapter0203.xlsx
+++ b/Assets/test260903/chapter0203.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e870389230b728a/ドキュメント/GitHub/utageTest/Assets/test260903/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="474" documentId="11_E10EE94338F254052E83A027A8BF203497349031" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D90E1CF4-E628-449F-B7F6-C8AEFE0BD8B7}"/>
+  <xr:revisionPtr revIDLastSave="507" documentId="11_E10EE94338F254052E83A027A8BF203497349031" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BD6AAD2-AB87-4ABA-A386-C3B7CD870583}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="855" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="190">
   <si>
     <t>Command</t>
   </si>
@@ -826,6 +826,32 @@
     <rPh sb="3" eb="5">
       <t>チュウオウ</t>
     </rPh>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>Bgm</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM_不穏</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM_日常コミカル</t>
+  </si>
+  <si>
+    <t>BGM_しんみり</t>
+  </si>
+  <si>
+    <t>StopBgm</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM_バトル</t>
+    <phoneticPr fontId="4"/>
+  </si>
+  <si>
+    <t>BGM_緊迫</t>
     <phoneticPr fontId="4"/>
   </si>
 </sst>
@@ -1142,7 +1168,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L1084"/>
+  <dimension ref="A1:L1092"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.44140625" customWidth="1"/>
@@ -1233,6 +1259,12 @@
       <c r="I4" s="1"/>
     </row>
     <row r="5" spans="1:12" ht="13.5" customHeight="1">
+      <c r="A5" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>184</v>
+      </c>
       <c r="H5" s="4"/>
       <c r="I5" s="1"/>
     </row>
@@ -1434,184 +1466,183 @@
       <c r="I24" s="5"/>
     </row>
     <row r="25" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A25" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>45</v>
+      <c r="A25" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>185</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="5"/>
     </row>
-    <row r="26" spans="1:10" ht="13.8" customHeight="1">
+    <row r="26" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A26" s="6" t="s">
+        <v>43</v>
+      </c>
       <c r="B26" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H26" s="1"/>
+      <c r="I26" s="5"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.8" customHeight="1">
+      <c r="B27" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="1"/>
-      <c r="I26" s="5" t="s">
+      <c r="C27" s="1"/>
+      <c r="I27" s="5" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B27" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C27" s="1" t="s">
+    <row r="28" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B28" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="I27" s="5" t="s">
+      <c r="I28" s="5" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A28" s="9" t="s">
+    <row r="29" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A29" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I28" s="5" t="s">
+      <c r="I29" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="J28" s="1"/>
-    </row>
-    <row r="29" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A29" s="1" t="s">
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A30" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-    </row>
-    <row r="30" spans="1:10" ht="30" customHeight="1">
-      <c r="B30" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C30" s="7" t="s">
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="1:10" ht="30" customHeight="1">
+      <c r="B31" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="I30" s="5" t="s">
+      <c r="I31" s="5" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A31" s="9" t="s">
+    <row r="32" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A32" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B32" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C31" s="1"/>
-      <c r="I31" s="5" t="s">
+      <c r="C32" s="1"/>
+      <c r="I32" s="5" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A32" s="1" t="s">
+    <row r="33" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A33" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-    </row>
-    <row r="33" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C33" s="1" t="s">
+      <c r="B33" s="1"/>
+      <c r="I33" s="1"/>
+      <c r="J33" s="1"/>
+    </row>
+    <row r="34" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A34" s="1"/>
+      <c r="B34" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C34" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I33" s="5" t="s">
+      <c r="I34" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="J33" s="1"/>
-    </row>
-    <row r="34" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A34" s="9" t="s">
+      <c r="J34" s="1"/>
+    </row>
+    <row r="35" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A35" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B35" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I34" s="5" t="s">
+      <c r="I35" s="5" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A35" s="1" t="s">
+    <row r="36" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A36" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="I35" s="1"/>
-    </row>
-    <row r="36" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B36" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C36" s="1" t="s">
+      <c r="I36" s="1"/>
+    </row>
+    <row r="37" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I36" s="5" t="s">
+      <c r="I37" s="5" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A37" s="9" t="s">
+    <row r="38" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A38" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B38" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I37" s="5" t="s">
+      <c r="I38" s="5" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A38" s="1" t="s">
+    <row r="39" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A39" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="I38" s="1"/>
-    </row>
-    <row r="39" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B39" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="C39" s="1" t="s">
+      <c r="I39" s="1"/>
+    </row>
+    <row r="40" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B40" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="I39" s="5" t="s">
+      <c r="I40" s="5" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A40" s="9" t="s">
+    <row r="41" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A41" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I40" s="5" t="s">
+      <c r="I41" s="5" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A41" s="1" t="s">
+    <row r="42" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A42" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="I41" s="1"/>
-    </row>
-    <row r="42" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B42" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="I42" s="5" t="s">
-        <v>62</v>
-      </c>
+      <c r="I42" s="1"/>
     </row>
     <row r="43" spans="1:10" ht="28.8" customHeight="1">
       <c r="B43" s="7" t="s">
@@ -1621,10 +1652,10 @@
         <v>32</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10" ht="30" customHeight="1">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" ht="28.8" customHeight="1">
       <c r="B44" s="7" t="s">
         <v>31</v>
       </c>
@@ -1632,10 +1663,10 @@
         <v>32</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10" ht="13.5" customHeight="1">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" ht="30" customHeight="1">
       <c r="B45" s="7" t="s">
         <v>31</v>
       </c>
@@ -1643,32 +1674,31 @@
         <v>32</v>
       </c>
       <c r="I45" s="5" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" ht="30" customHeight="1">
+      <c r="A46" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C46" s="7"/>
+      <c r="I46" s="5"/>
+    </row>
+    <row r="47" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B47" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="I47" s="5" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B46" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I46" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B47" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="I47" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" ht="30.6" customHeight="1">
+    <row r="48" spans="1:10" ht="13.5" customHeight="1">
       <c r="B48" s="7" t="s">
         <v>31</v>
       </c>
@@ -1676,11 +1706,10 @@
         <v>67</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10" ht="31.2" customHeight="1">
-      <c r="A49" s="1"/>
+        <v>66</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" ht="28.8" customHeight="1">
       <c r="B49" s="7" t="s">
         <v>31</v>
       </c>
@@ -1688,51 +1717,51 @@
         <v>67</v>
       </c>
       <c r="I49" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" ht="30.6" customHeight="1">
+      <c r="B50" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I50" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" ht="31.2" customHeight="1">
+      <c r="A51" s="1"/>
+      <c r="B51" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="I51" s="5" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A50" s="9" t="s">
+    <row r="52" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A52" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I50" s="5" t="s">
+      <c r="I52" s="5" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A51" s="1" t="s">
+    <row r="53" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A53" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-    </row>
-    <row r="52" spans="1:10" ht="31.8" customHeight="1">
-      <c r="B52" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C52" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I52" s="5" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="53" spans="1:10" ht="30.6" customHeight="1">
-      <c r="B53" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C53" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I53" s="5" t="s">
-        <v>75</v>
-      </c>
+      <c r="I53" s="1"/>
       <c r="J53" s="1"/>
     </row>
-    <row r="54" spans="1:10" ht="31.2" customHeight="1">
+    <row r="54" spans="1:10" ht="31.8" customHeight="1">
       <c r="B54" s="7" t="s">
         <v>31</v>
       </c>
@@ -1740,12 +1769,10 @@
         <v>74</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="J54" s="1"/>
-    </row>
-    <row r="55" spans="1:10" ht="30" customHeight="1">
-      <c r="A55" s="1"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10" ht="30.6" customHeight="1">
       <c r="B55" s="7" t="s">
         <v>31</v>
       </c>
@@ -1753,12 +1780,11 @@
         <v>74</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J55" s="1"/>
     </row>
-    <row r="56" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A56" s="1"/>
+    <row r="56" spans="1:10" ht="31.2" customHeight="1">
       <c r="B56" s="7" t="s">
         <v>31</v>
       </c>
@@ -1766,11 +1792,12 @@
         <v>74</v>
       </c>
       <c r="I56" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="J56" s="1"/>
     </row>
-    <row r="57" spans="1:10" ht="13.5" customHeight="1">
+    <row r="57" spans="1:10" ht="30" customHeight="1">
+      <c r="A57" s="1"/>
       <c r="B57" s="7" t="s">
         <v>31</v>
       </c>
@@ -1778,10 +1805,12 @@
         <v>74</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="58" spans="1:10" ht="30" customHeight="1">
+        <v>77</v>
+      </c>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A58" s="1"/>
       <c r="B58" s="7" t="s">
         <v>31</v>
       </c>
@@ -1789,300 +1818,293 @@
         <v>74</v>
       </c>
       <c r="I58" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="J58" s="1"/>
+    </row>
+    <row r="59" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B59" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I59" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10" ht="30" customHeight="1">
+      <c r="B60" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I60" s="5" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A59" s="1"/>
-      <c r="B59" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I59" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="60" spans="1:10" ht="30" customHeight="1">
-      <c r="A60" s="1"/>
-      <c r="B60" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="I60" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
     <row r="61" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A61" s="1"/>
       <c r="B61" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="62" spans="1:10" ht="28.2" customHeight="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10" ht="30" customHeight="1">
+      <c r="A62" s="1"/>
       <c r="B62" s="7" t="s">
         <v>33</v>
       </c>
       <c r="I62" s="5" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B63" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I63" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B64" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="I64" s="5" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A63" s="1"/>
-      <c r="B63" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" s="7" t="s">
+    <row r="65" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A65" s="1"/>
+      <c r="B65" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C65" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I63" s="5" t="s">
+      <c r="I65" s="5" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A64" s="9" t="s">
+    <row r="66" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A66" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="I64" s="5" t="s">
+      <c r="I66" s="5" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="65" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A65" s="9" t="s">
+    <row r="67" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A67" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B67" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="C65" s="1"/>
-      <c r="I65" s="5" t="s">
+      <c r="C67" s="1"/>
+      <c r="I67" s="5" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="66" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A66" s="1" t="s">
+    <row r="68" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A68" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="I66" s="1"/>
-    </row>
-    <row r="67" spans="1:9" ht="28.8" customHeight="1">
-      <c r="B67" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C67" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="I67" s="5" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="68" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A68" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>92</v>
-      </c>
+      <c r="B68" s="1"/>
       <c r="C68" s="1"/>
       <c r="I68" s="1"/>
     </row>
-    <row r="69" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A69" s="1" t="s">
+    <row r="69" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B69" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C69" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="I69" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A70" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C70" s="1"/>
+      <c r="I70" s="1"/>
+    </row>
+    <row r="71" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A71" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B69" s="1"/>
-      <c r="I69" s="1"/>
-    </row>
-    <row r="70" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A70" s="1"/>
-      <c r="B70" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C70" s="9" t="s">
+      <c r="B71" s="1"/>
+      <c r="I71" s="1"/>
+    </row>
+    <row r="72" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A72" s="1"/>
+      <c r="B72" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C72" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1" t="s">
+      <c r="H72" s="1"/>
+      <c r="I72" s="1" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="71" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A71" s="9" t="s">
+    <row r="73" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A73" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B73" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="C71" s="1"/>
-      <c r="I71" s="1"/>
-    </row>
-    <row r="72" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A72" s="1" t="s">
+      <c r="C73" s="1"/>
+      <c r="I73" s="1"/>
+    </row>
+    <row r="74" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A74" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="I72" s="1"/>
-    </row>
-    <row r="73" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A73" s="1"/>
-      <c r="B73" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C73" s="9" t="s">
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="I74" s="1"/>
+    </row>
+    <row r="75" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A75" s="1"/>
+      <c r="B75" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C75" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="I73" s="1" t="s">
+      <c r="I75" s="1" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="74" spans="1:9" ht="30.6" customHeight="1">
-      <c r="A74" s="1"/>
-      <c r="B74" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C74" s="6" t="s">
+    <row r="76" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A76" s="1"/>
+      <c r="B76" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C76" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="H74" s="1"/>
-      <c r="I74" s="5" t="s">
+      <c r="H76" s="1"/>
+      <c r="I76" s="5" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="75" spans="1:9" ht="31.8" customHeight="1">
-      <c r="B75" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C75" s="1"/>
-      <c r="I75" s="5" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" ht="30" customHeight="1">
-      <c r="B76" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="C76" s="1"/>
-      <c r="I76" s="5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" ht="30.6" customHeight="1">
+    <row r="77" spans="1:9" ht="31.8" customHeight="1">
       <c r="B77" s="7" t="s">
         <v>33</v>
       </c>
       <c r="C77" s="1"/>
       <c r="I77" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="78" spans="1:9" ht="28.2" customHeight="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" ht="30" customHeight="1">
       <c r="B78" s="7" t="s">
         <v>33</v>
       </c>
       <c r="C78" s="1"/>
       <c r="I78" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B79" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C79" s="1"/>
+      <c r="I79" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A80" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B80" s="7"/>
+      <c r="C80" s="1"/>
+      <c r="I80" s="5"/>
+    </row>
+    <row r="81" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B81" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C81" s="1"/>
+      <c r="I81" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="79" spans="1:9" ht="28.2" customHeight="1">
-      <c r="A79" s="6" t="s">
+    <row r="82" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A82" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B79" s="7" t="s">
+      <c r="B82" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C79" s="1"/>
-      <c r="I79" s="5"/>
-    </row>
-    <row r="80" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A80" s="7" t="s">
+      <c r="C82" s="1"/>
+      <c r="I82" s="5"/>
+    </row>
+    <row r="83" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A83" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B80" s="7" t="s">
+      <c r="B83" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G80">
+      <c r="G83">
         <v>1</v>
       </c>
-      <c r="I80" s="1"/>
-    </row>
-    <row r="81" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A81" s="7"/>
-      <c r="B81" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C81" s="6" t="s">
+      <c r="I83" s="1"/>
+    </row>
+    <row r="84" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A84" s="7"/>
+      <c r="B84" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="I81" s="1"/>
-    </row>
-    <row r="82" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A82" s="3" t="s">
+      <c r="I84" s="1"/>
+    </row>
+    <row r="85" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A85" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B82" s="7" t="s">
+      <c r="B85" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="I82" s="1"/>
-    </row>
-    <row r="83" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A83" s="3"/>
-      <c r="B83" s="6" t="s">
+      <c r="I85" s="1"/>
+    </row>
+    <row r="86" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A86" s="3"/>
+      <c r="B86" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="C83" s="1" t="s">
+      <c r="C86" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D83" s="9" t="s">
+      <c r="D86" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="I83" s="1"/>
-    </row>
-    <row r="84" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A84" s="3"/>
-      <c r="B84" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D84" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I84" s="1"/>
-    </row>
-    <row r="85" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A85" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G85">
-        <v>1</v>
-      </c>
-      <c r="I85" s="1"/>
-    </row>
-    <row r="86" spans="1:10" ht="28.2" customHeight="1">
-      <c r="B86" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C86" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D86" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="I86" s="5" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="87" spans="1:10" ht="28.2" customHeight="1">
+      <c r="I86" s="1"/>
+    </row>
+    <row r="87" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A87" s="3"/>
       <c r="B87" s="6" t="s">
         <v>31</v>
       </c>
@@ -2092,38 +2114,35 @@
       <c r="D87" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I87" s="5" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="88" spans="1:10" ht="27.6" customHeight="1">
-      <c r="B88" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C88" s="6" t="s">
+      <c r="I87" s="1"/>
+    </row>
+    <row r="88" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A88" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="I88" s="1"/>
+    </row>
+    <row r="89" spans="1:10" ht="28.2" customHeight="1">
+      <c r="B89" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C89" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D88" s="6" t="s">
+      <c r="D89" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I88" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="J88" s="1"/>
-    </row>
-    <row r="89" spans="1:10" ht="27.6" customHeight="1">
-      <c r="A89" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="B89" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C89" s="6"/>
-      <c r="D89" s="6"/>
-      <c r="I89" s="5"/>
-      <c r="J89" s="1"/>
-    </row>
-    <row r="90" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I89" s="5" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" ht="28.2" customHeight="1">
       <c r="B90" s="6" t="s">
         <v>31</v>
       </c>
@@ -2133,35 +2152,38 @@
       <c r="D90" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="I90" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="91" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I90" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" ht="27.6" customHeight="1">
       <c r="B91" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C91" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D91" s="9" t="s">
-        <v>106</v>
+        <v>31</v>
+      </c>
+      <c r="C91" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D91" s="6" t="s">
+        <v>102</v>
       </c>
       <c r="I91" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="92" spans="1:10" ht="13.5" customHeight="1">
+        <v>107</v>
+      </c>
+      <c r="J91" s="1"/>
+    </row>
+    <row r="92" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A92" s="8" t="s">
+        <v>23</v>
+      </c>
       <c r="B92" s="6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C92" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="I92" s="1"/>
-    </row>
-    <row r="93" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A93" s="1"/>
+        <v>109</v>
+      </c>
+      <c r="C92" s="6"/>
+      <c r="D92" s="6"/>
+      <c r="I92" s="5"/>
+      <c r="J92" s="1"/>
+    </row>
+    <row r="93" spans="1:10" ht="13.5" customHeight="1">
       <c r="B93" s="6" t="s">
         <v>31</v>
       </c>
@@ -2169,62 +2191,70 @@
         <v>47</v>
       </c>
       <c r="D93" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="I93" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="94" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B94" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C94" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>106</v>
+      </c>
+      <c r="I94" s="5" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="95" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B95" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C95" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I95" s="1"/>
+    </row>
+    <row r="96" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A96" s="1"/>
+      <c r="B96" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C96" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D96" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I93" s="5" t="s">
+      <c r="I96" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="J93" s="1"/>
-    </row>
-    <row r="94" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A94" s="1"/>
-      <c r="B94" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C94" s="6" t="s">
+      <c r="J96" s="1"/>
+    </row>
+    <row r="97" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A97" s="1"/>
+      <c r="B97" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C97" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D94" s="6" t="s">
+      <c r="D97" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="I94" s="5" t="s">
+      <c r="I97" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="J94" s="1"/>
-    </row>
-    <row r="95" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A95" s="7" t="s">
+      <c r="J97" s="1"/>
+    </row>
+    <row r="98" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A98" s="7" t="s">
         <v>100</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="G95">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="96" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A96" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B96" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="I96" s="1"/>
-    </row>
-    <row r="97" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A97" s="3"/>
-      <c r="B97" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C97" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="I97" s="1"/>
-    </row>
-    <row r="98" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A98" s="6" t="s">
-        <v>21</v>
       </c>
       <c r="B98" s="7" t="s">
         <v>22</v>
@@ -2232,151 +2262,145 @@
       <c r="G98">
         <v>1</v>
       </c>
-      <c r="I98" s="1"/>
-    </row>
-    <row r="99" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A99" s="8" t="s">
+    </row>
+    <row r="99" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A99" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B99" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="I99" s="1"/>
+    </row>
+    <row r="100" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A100" s="3"/>
+      <c r="B100" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C100" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="I100" s="1"/>
+    </row>
+    <row r="101" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A101" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="I101" s="1"/>
+    </row>
+    <row r="102" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A102" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B99" s="1" t="s">
+      <c r="B102" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C99" s="9" t="b">
+      <c r="C102" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="I99" s="1"/>
-    </row>
-    <row r="100" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B100" s="7" t="s">
+      <c r="I102" s="1"/>
+    </row>
+    <row r="103" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A103" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C103" s="9"/>
+      <c r="I103" s="1"/>
+    </row>
+    <row r="104" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B104" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C100" s="1"/>
-      <c r="I100" s="1" t="s">
+      <c r="C104" s="1"/>
+      <c r="I104" s="1" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="101" spans="1:9" ht="30" customHeight="1">
-      <c r="B101" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="C101" s="7" t="s">
+    <row r="105" spans="1:10" ht="30" customHeight="1">
+      <c r="B105" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="C105" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="I101" s="5" t="s">
+      <c r="I105" s="5" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="102" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A102" s="9" t="s">
+    <row r="106" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A106" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B102" s="1" t="s">
+      <c r="B106" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="C102" s="1"/>
-      <c r="I102" s="1" t="s">
+      <c r="C106" s="1"/>
+      <c r="I106" s="1" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="103" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A103" s="9" t="s">
+    <row r="107" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A107" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B103" s="1" t="s">
+      <c r="B107" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="I103" s="1" t="s">
+      <c r="I107" s="1" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="104" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A104" s="1" t="s">
+    <row r="108" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A108" s="1" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="105" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A105" s="9" t="s">
+    <row r="109" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A109" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B105" s="1" t="s">
+      <c r="B109" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C105" s="1"/>
-      <c r="I105" s="1"/>
-    </row>
-    <row r="106" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A106" s="1" t="s">
+      <c r="C109" s="1"/>
+      <c r="I109" s="1"/>
+    </row>
+    <row r="110" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A110" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="B106" s="1"/>
-      <c r="C106" s="1"/>
-      <c r="I106" s="1"/>
-    </row>
-    <row r="107" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A107" s="9" t="s">
+      <c r="B110" s="1"/>
+      <c r="C110" s="1"/>
+      <c r="I110" s="1"/>
+    </row>
+    <row r="111" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A111" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="B107" s="1" t="s">
+      <c r="B111" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="C107" s="1"/>
-      <c r="I107" s="1"/>
-    </row>
-    <row r="108" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A108" s="1" t="s">
+      <c r="C111" s="1"/>
+      <c r="I111" s="1"/>
+    </row>
+    <row r="112" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A112" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="B108" s="1"/>
-      <c r="C108" s="1"/>
-      <c r="I108" s="1"/>
-    </row>
-    <row r="109" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A109" s="1"/>
-      <c r="B109" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C109" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I109" s="10" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="110" spans="1:9" ht="30" customHeight="1">
-      <c r="A110" s="1"/>
-      <c r="B110" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C110" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I110" s="10" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="111" spans="1:9" ht="30" customHeight="1">
-      <c r="B111" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C111" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I111" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="112" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B112" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C112" s="6" t="s">
-        <v>32</v>
-      </c>
-      <c r="I112" s="5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B112" s="1"/>
+      <c r="C112" s="1"/>
+      <c r="I112" s="1"/>
+    </row>
+    <row r="113" spans="1:9" ht="28.8" customHeight="1">
       <c r="A113" s="1"/>
       <c r="B113" s="6" t="s">
         <v>31</v>
@@ -2384,303 +2408,303 @@
       <c r="C113" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="I113" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="114" spans="1:9" ht="13.5" customHeight="1">
+      <c r="I113" s="10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" ht="30" customHeight="1">
       <c r="A114" s="1"/>
       <c r="B114" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C114" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I114" s="10" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9" ht="30" customHeight="1">
+      <c r="B115" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I115" s="5" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B116" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C116" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I116" s="5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A117" s="1"/>
+      <c r="B117" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C117" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="I117" s="5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A118" s="1"/>
+      <c r="B118" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C118" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="H114" s="1"/>
-      <c r="I114" s="5" t="s">
+      <c r="H118" s="1"/>
+      <c r="I118" s="5" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="115" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B115" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C115" s="6" t="s">
+    <row r="119" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A119" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B119" s="6"/>
+      <c r="C119" s="6"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="5"/>
+    </row>
+    <row r="120" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B120" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C120" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I115" s="5" t="s">
+      <c r="I120" s="5" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="116" spans="1:9" ht="30.6" customHeight="1">
-      <c r="A116" s="6" t="s">
+    <row r="121" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A121" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B116" s="7" t="s">
+      <c r="B121" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C116" s="6"/>
-      <c r="I116" s="5"/>
-    </row>
-    <row r="117" spans="1:9" ht="30.6" customHeight="1">
-      <c r="A117" s="8" t="s">
+      <c r="C121" s="6"/>
+      <c r="I121" s="5"/>
+    </row>
+    <row r="122" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A122" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B117" s="8" t="s">
+      <c r="B122" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="C117" s="6"/>
-      <c r="I117" s="5"/>
-    </row>
-    <row r="118" spans="1:9" ht="30.6" customHeight="1">
-      <c r="A118" s="6" t="s">
+      <c r="C122" s="6"/>
+      <c r="I122" s="5"/>
+    </row>
+    <row r="123" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A123" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B118" s="7" t="s">
+      <c r="B123" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D118" s="6" t="s">
+      <c r="D123" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="I118" s="5"/>
-    </row>
-    <row r="119" spans="1:9" ht="30.6" customHeight="1">
-      <c r="A119" s="6" t="s">
+      <c r="I123" s="5"/>
+    </row>
+    <row r="124" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A124" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="B119" s="6" t="s">
+      <c r="B124" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C119" s="6"/>
-      <c r="G119">
+      <c r="C124" s="6"/>
+      <c r="G124">
         <v>1</v>
       </c>
-      <c r="I119" s="5"/>
-    </row>
-    <row r="120" spans="1:9" ht="30.6" customHeight="1">
-      <c r="A120" s="6"/>
-      <c r="B120" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C120" s="6" t="s">
+      <c r="I124" s="5"/>
+    </row>
+    <row r="125" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A125" s="6"/>
+      <c r="B125" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C125" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="I120" s="5"/>
-    </row>
-    <row r="121" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B121" s="7" t="s">
+      <c r="I125" s="5"/>
+    </row>
+    <row r="126" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B126" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C121" s="1"/>
-      <c r="I121" s="5" t="s">
+      <c r="C126" s="1"/>
+      <c r="I126" s="5" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="122" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A122" s="3" t="s">
+    <row r="127" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A127" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B122" s="7" t="s">
+      <c r="B127" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="C122" s="1"/>
-      <c r="I122" s="5"/>
-    </row>
-    <row r="123" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A123" s="9" t="s">
+      <c r="C127" s="1"/>
+      <c r="I127" s="5"/>
+    </row>
+    <row r="128" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A128" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B123" s="6" t="s">
+      <c r="B128" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="C123" s="1"/>
-      <c r="G123">
+      <c r="C128" s="1"/>
+      <c r="G128">
         <v>1</v>
       </c>
-      <c r="I123" s="1"/>
-    </row>
-    <row r="124" spans="1:9" ht="13.5" customHeight="1">
-      <c r="I124" s="1" t="s">
+      <c r="I128" s="1"/>
+    </row>
+    <row r="129" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I129" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="125" spans="1:9" ht="27.6" customHeight="1">
-      <c r="I125" s="5" t="s">
+    <row r="130" spans="1:10" ht="27.6" customHeight="1">
+      <c r="I130" s="5" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="126" spans="1:9" ht="27.6" customHeight="1">
-      <c r="A126" s="7" t="s">
+    <row r="131" spans="1:10" ht="27.6" customHeight="1">
+      <c r="A131" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B126" s="7" t="s">
+      <c r="B131" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G126">
+      <c r="G131">
         <v>1</v>
       </c>
-      <c r="I126" s="5"/>
-    </row>
-    <row r="127" spans="1:9" ht="28.8" customHeight="1">
-      <c r="I127" s="5" t="s">
+      <c r="I131" s="5"/>
+    </row>
+    <row r="132" spans="1:10" ht="28.8" customHeight="1">
+      <c r="I132" s="5" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="128" spans="1:9" ht="28.8" customHeight="1">
-      <c r="A128" s="11" t="s">
+    <row r="133" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A133" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B128" s="7" t="s">
+      <c r="B133" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="I128" s="5"/>
-    </row>
-    <row r="129" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A129" s="6" t="s">
+      <c r="I133" s="5"/>
+    </row>
+    <row r="134" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A134" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B129" s="7" t="s">
+      <c r="B134" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G129">
+      <c r="G134">
         <v>1</v>
       </c>
-      <c r="I129" s="5"/>
-    </row>
-    <row r="130" spans="1:10" ht="28.8" customHeight="1">
-      <c r="A130" s="8" t="s">
+      <c r="I134" s="5"/>
+    </row>
+    <row r="135" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A135" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B130" s="7" t="s">
+      <c r="B135" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="C130" s="6" t="b">
+      <c r="C135" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="I130" s="5"/>
-    </row>
-    <row r="131" spans="1:10" ht="30.6" customHeight="1">
-      <c r="I131" s="5" t="s">
+      <c r="I135" s="5"/>
+    </row>
+    <row r="136" spans="1:10" ht="28.8" customHeight="1">
+      <c r="A136" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B136" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="C136" s="6"/>
+      <c r="I136" s="5"/>
+    </row>
+    <row r="137" spans="1:10" ht="30.6" customHeight="1">
+      <c r="I137" s="5" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="132" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B132" s="7" t="s">
+    <row r="138" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B138" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="I132" s="5" t="s">
+      <c r="I138" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="133" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A133" s="9" t="s">
+    <row r="139" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A139" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="B133" s="1" t="s">
+      <c r="B139" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="C133" s="1"/>
-      <c r="I133" s="1" t="s">
+      <c r="C139" s="1"/>
+      <c r="I139" s="1" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="134" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A134" s="1" t="s">
+    <row r="140" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A140" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B134" s="1"/>
-      <c r="C134" s="1"/>
-      <c r="I134" s="1"/>
-    </row>
-    <row r="135" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B135" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C135" s="6" t="s">
+      <c r="B140" s="1"/>
+      <c r="C140" s="1"/>
+      <c r="I140" s="1"/>
+    </row>
+    <row r="141" spans="1:10" ht="13.5" customHeight="1">
+      <c r="B141" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C141" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I135" s="5" t="s">
+      <c r="I141" s="5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="136" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B136" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C136" s="6" t="s">
+    <row r="142" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B142" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C142" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I136" s="5" t="s">
+      <c r="I142" s="5" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="137" spans="1:10" ht="30" customHeight="1">
-      <c r="A137" s="1"/>
-      <c r="B137" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C137" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I137" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="J137" s="1"/>
-    </row>
-    <row r="138" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A138" s="1"/>
-      <c r="B138" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C138" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="I138" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J138" s="1"/>
-    </row>
-    <row r="139" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A139" s="1"/>
-      <c r="B139" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C139" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="I139" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="J139" s="1"/>
-    </row>
-    <row r="140" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B140" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C140" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="I140" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="141" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A141" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B141" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="I141" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="142" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A142" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="143" spans="1:10" ht="28.8" customHeight="1">
+    <row r="143" spans="1:10" ht="30" customHeight="1">
+      <c r="A143" s="1"/>
       <c r="B143" s="6" t="s">
         <v>31</v>
       </c>
@@ -2688,30 +2712,35 @@
         <v>47</v>
       </c>
       <c r="I143" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="144" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A144" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B144" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="C144" s="1"/>
-      <c r="I144" s="5" t="s">
-        <v>155</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="J143" s="1"/>
+    </row>
+    <row r="144" spans="1:10" ht="30" customHeight="1">
+      <c r="A144" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B144" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="C144" s="6"/>
+      <c r="I144" s="5"/>
+      <c r="J144" s="1"/>
     </row>
     <row r="145" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A145" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="B145" s="1"/>
-      <c r="C145" s="1"/>
-      <c r="I145" s="1"/>
-    </row>
-    <row r="146" spans="1:10" ht="30" customHeight="1">
+      <c r="A145" s="1"/>
+      <c r="B145" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C145" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I145" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="J145" s="1"/>
+    </row>
+    <row r="146" spans="1:10" ht="13.5" customHeight="1">
       <c r="A146" s="1"/>
       <c r="B146" s="6" t="s">
         <v>147</v>
@@ -2719,81 +2748,70 @@
       <c r="C146" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="I146" s="10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="147" spans="1:10" ht="30.6" customHeight="1">
-      <c r="A147" s="1"/>
+      <c r="I146" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="J146" s="1"/>
+    </row>
+    <row r="147" spans="1:10" ht="13.5" customHeight="1">
       <c r="B147" s="6" t="s">
-        <v>147</v>
+        <v>31</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>148</v>
+        <v>47</v>
       </c>
       <c r="I147" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="J147" s="1"/>
+        <v>150</v>
+      </c>
     </row>
     <row r="148" spans="1:10" ht="13.5" customHeight="1">
-      <c r="B148" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C148" s="6" t="s">
+      <c r="A148" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="I148" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="149" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A149" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="150" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B150" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C150" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="I148" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="149" spans="1:10" ht="30" customHeight="1">
-      <c r="B149" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C149" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="I149" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="150" spans="1:10" ht="31.2" customHeight="1">
-      <c r="A150" s="1"/>
-      <c r="B150" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C150" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="I150" s="10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="151" spans="1:10" ht="28.2" customHeight="1">
-      <c r="A151" s="1"/>
-      <c r="B151" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C151" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="I151" s="10" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="152" spans="1:10" ht="28.8" customHeight="1">
-      <c r="B152" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="C152" s="6" t="s">
-        <v>148</v>
-      </c>
-      <c r="I152" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="153" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I150" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="151" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A151" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="C151" s="1"/>
+      <c r="I151" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="152" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A152" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="B152" s="1"/>
+      <c r="C152" s="1"/>
+      <c r="I152" s="1"/>
+    </row>
+    <row r="153" spans="1:10" ht="30" customHeight="1">
       <c r="A153" s="1"/>
       <c r="B153" s="6" t="s">
         <v>147</v>
@@ -2801,47 +2819,46 @@
       <c r="C153" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="I153" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="154" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I153" s="10" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="154" spans="1:10" ht="30.6" customHeight="1">
       <c r="A154" s="1"/>
       <c r="B154" s="6" t="s">
-        <v>31</v>
+        <v>147</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>67</v>
+        <v>148</v>
       </c>
       <c r="I154" s="5" t="s">
-        <v>164</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="J154" s="1"/>
     </row>
     <row r="155" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A155" s="1"/>
       <c r="B155" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C155" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="H155" s="1"/>
       <c r="I155" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="156" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A156" s="8" t="s">
-        <v>23</v>
-      </c>
+        <v>158</v>
+      </c>
+    </row>
+    <row r="156" spans="1:10" ht="30" customHeight="1">
       <c r="B156" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="C156" s="6"/>
-      <c r="H156" s="1"/>
-      <c r="I156" s="5"/>
-    </row>
-    <row r="157" spans="1:10" ht="13.2" customHeight="1">
+        <v>147</v>
+      </c>
+      <c r="C156" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I156" s="5" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="157" spans="1:10" ht="31.2" customHeight="1">
       <c r="A157" s="1"/>
       <c r="B157" s="6" t="s">
         <v>147</v>
@@ -2849,217 +2866,304 @@
       <c r="C157" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="H157" s="1"/>
-      <c r="I157" s="5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="158" spans="1:10" ht="13.5" customHeight="1">
+      <c r="I157" s="10" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="158" spans="1:10" ht="28.2" customHeight="1">
+      <c r="A158" s="1"/>
       <c r="B158" s="6" t="s">
         <v>147</v>
       </c>
       <c r="C158" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I158" s="10" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="159" spans="1:10" ht="28.8" customHeight="1">
+      <c r="B159" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C159" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I159" s="5" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="160" spans="1:10" ht="13.5" customHeight="1">
+      <c r="A160" s="1"/>
+      <c r="B160" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C160" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="I160" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="161" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A161" s="1"/>
+      <c r="B161" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C161" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="I161" s="5" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="162" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A162" s="1"/>
+      <c r="B162" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C162" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="H162" s="1"/>
+      <c r="I162" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="163" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A163" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="B163" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C163" s="6"/>
+      <c r="H163" s="1"/>
+      <c r="I163" s="5"/>
+    </row>
+    <row r="164" spans="1:9" ht="13.2" customHeight="1">
+      <c r="A164" s="1"/>
+      <c r="B164" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C164" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="H164" s="1"/>
+      <c r="I164" s="5" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="165" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B165" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C165" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="I158" s="1"/>
-    </row>
-    <row r="159" spans="1:10" ht="13.5" customHeight="1">
-      <c r="A159" s="8" t="s">
+      <c r="I165" s="1"/>
+    </row>
+    <row r="166" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A166" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B159" s="6" t="s">
+      <c r="B166" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="C159" s="6"/>
-      <c r="I159" s="1"/>
-    </row>
-    <row r="160" spans="1:10" ht="30.6" customHeight="1">
-      <c r="I160" s="5" t="s">
+      <c r="C166" s="6"/>
+      <c r="I166" s="1"/>
+    </row>
+    <row r="167" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A167" s="8"/>
+      <c r="B167" s="6"/>
+      <c r="C167" s="6"/>
+      <c r="I167" s="1"/>
+    </row>
+    <row r="168" spans="1:9" ht="30.6" customHeight="1">
+      <c r="A168" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B168" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="I168" s="5" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="161" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B161" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C161" s="6" t="s">
+    <row r="169" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B169" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C169" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I161" s="5" t="s">
+      <c r="I169" s="5" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="162" spans="1:9" ht="30.6" customHeight="1">
-      <c r="B162" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C162" s="6" t="s">
+    <row r="170" spans="1:9" ht="30.6" customHeight="1">
+      <c r="B170" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C170" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I162" s="5" t="s">
+      <c r="I170" s="5" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="163" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B163" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C163" s="6" t="s">
-        <v>74</v>
-      </c>
-      <c r="I163" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="164" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A164" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B164" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="I164" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="165" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A165" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="B165" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="I165" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="166" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A166" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="167" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A167" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B167" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="168" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A168" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="169" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A169" s="9" t="s">
-        <v>86</v>
-      </c>
-      <c r="B169" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="170" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A170" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="171" spans="1:9" ht="28.8" customHeight="1">
+    <row r="171" spans="1:9" ht="13.5" customHeight="1">
       <c r="B171" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C171" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I171" s="10" t="s">
+      <c r="I171" s="5" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A172" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="I172" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A173" s="9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="I173" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A174" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A175" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A176" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A177" s="9" t="s">
+        <v>86</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A178" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="28.8" customHeight="1">
+      <c r="B179" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C179" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="I179" s="10" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="172" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B172" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C172" s="6" t="s">
+    <row r="180" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B180" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C180" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="I172" s="9" t="s">
+      <c r="I180" s="9" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="173" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A173" s="6" t="s">
+    <row r="181" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A181" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B173" s="6" t="s">
+      <c r="B181" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="174" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A174" s="6" t="s">
+    <row r="182" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A182" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B174" s="9" t="s">
+      <c r="B182" s="9" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="175" spans="1:9" ht="13.5" customHeight="1">
-      <c r="B175" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C175" s="6" t="s">
+    <row r="183" spans="1:9" ht="13.5" customHeight="1">
+      <c r="B183" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C183" s="6" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="176" spans="1:9" ht="13.5" customHeight="1">
-      <c r="A176" s="7" t="s">
+    <row r="184" spans="1:9" ht="13.5" customHeight="1">
+      <c r="A184" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B176" s="7" t="s">
+      <c r="B184" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G176">
+      <c r="G184">
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="178" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="179" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="180" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="181" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="182" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="183" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="184" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="185" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="186" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="187" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="188" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="189" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="190" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="191" spans="1:2" ht="13.5" customHeight="1">
-      <c r="A191" s="1" t="s">
+    <row r="185" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="186" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="187" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="188" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="189" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="190" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="191" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="192" spans="1:9" ht="13.5" customHeight="1"/>
+    <row r="193" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="194" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="195" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="196" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="197" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="198" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="199" spans="1:2" ht="13.5" customHeight="1">
+      <c r="A199" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B191" s="1" t="s">
+      <c r="B199" s="1" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="192" spans="1:2" ht="13.5" customHeight="1"/>
-    <row r="193" ht="13.5" customHeight="1"/>
-    <row r="194" ht="13.5" customHeight="1"/>
-    <row r="195" ht="13.5" customHeight="1"/>
-    <row r="196" ht="13.5" customHeight="1"/>
-    <row r="197" ht="13.5" customHeight="1"/>
-    <row r="198" ht="13.5" customHeight="1"/>
-    <row r="199" ht="13.5" customHeight="1"/>
-    <row r="200" ht="13.5" customHeight="1"/>
-    <row r="201" ht="13.5" customHeight="1"/>
-    <row r="202" ht="13.5" customHeight="1"/>
-    <row r="203" ht="13.5" customHeight="1"/>
-    <row r="204" ht="13.5" customHeight="1"/>
-    <row r="205" ht="13.5" customHeight="1"/>
-    <row r="206" ht="13.5" customHeight="1"/>
-    <row r="207" ht="13.5" customHeight="1"/>
-    <row r="208" ht="13.5" customHeight="1"/>
+    <row r="200" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="201" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="202" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="203" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="204" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="205" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="206" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="207" spans="1:2" ht="13.5" customHeight="1"/>
+    <row r="208" spans="1:2" ht="13.5" customHeight="1"/>
     <row r="209" ht="13.5" customHeight="1"/>
     <row r="210" ht="13.5" customHeight="1"/>
     <row r="211" ht="13.5" customHeight="1"/>
@@ -3936,6 +4040,14 @@
     <row r="1082" ht="13.5" customHeight="1"/>
     <row r="1083" ht="13.5" customHeight="1"/>
     <row r="1084" ht="13.5" customHeight="1"/>
+    <row r="1085" ht="13.5" customHeight="1"/>
+    <row r="1086" ht="13.5" customHeight="1"/>
+    <row r="1087" ht="13.5" customHeight="1"/>
+    <row r="1088" ht="13.5" customHeight="1"/>
+    <row r="1089" ht="13.5" customHeight="1"/>
+    <row r="1090" ht="13.5" customHeight="1"/>
+    <row r="1091" ht="13.5" customHeight="1"/>
+    <row r="1092" ht="13.5" customHeight="1"/>
   </sheetData>
   <phoneticPr fontId="4"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
